--- a/システム開発演習/020-内部_プログラミング設計/022-クラス仕様書/Serviceのクラス仕様書(ItemSerchService).xlsx
+++ b/システム開発演習/020-内部_プログラミング設計/022-クラス仕様書/Serviceのクラス仕様書(ItemSerchService).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891CCD68-5095-4602-9F3E-598976B223E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD94EF4B-A464-4FD1-AF1F-43518A335EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -304,10 +304,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.try</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>メソッド：findAll</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -320,29 +316,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メソッド：findByBoth</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>呼び出すメソッドの条件分岐</t>
     <rPh sb="0" eb="1">
       <t>ヨ</t>
     </rPh>
     <rPh sb="2" eb="3">
       <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>上記以外の場合</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -407,13 +386,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>引数：categoryId</t>
-    <rPh sb="0" eb="2">
-      <t>ヒキスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>変数名：itemList</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -459,6 +431,13 @@
     <t>商品検索を行い、商品の詳細情報を返すServiceクラス</t>
     <rPh sb="5" eb="6">
       <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.try句</t>
+    <rPh sb="5" eb="6">
+      <t>ク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -852,66 +831,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -950,6 +869,66 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1301,85 +1280,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="42" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="41" t="s">
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="42" t="s">
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="41" t="s">
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
-      <c r="AQ1" s="42" t="s">
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="42"/>
-      <c r="AS1" s="42"/>
-      <c r="AT1" s="41" t="s">
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AU1" s="41"/>
-      <c r="AV1" s="41"/>
-      <c r="AW1" s="41"/>
-      <c r="AX1" s="41"/>
-      <c r="AY1" s="41"/>
-      <c r="AZ1" s="41"/>
-      <c r="BA1" s="42" t="s">
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="50"/>
+      <c r="AX1" s="50"/>
+      <c r="AY1" s="50"/>
+      <c r="AZ1" s="50"/>
+      <c r="BA1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="BB1" s="42"/>
-      <c r="BC1" s="42"/>
-      <c r="BD1" s="39">
+      <c r="BB1" s="49"/>
+      <c r="BC1" s="49"/>
+      <c r="BD1" s="51">
         <v>45000</v>
       </c>
-      <c r="BE1" s="39"/>
-      <c r="BF1" s="39"/>
-      <c r="BG1" s="39"/>
-      <c r="BH1" s="39"/>
-      <c r="BI1" s="39"/>
+      <c r="BE1" s="51"/>
+      <c r="BF1" s="51"/>
+      <c r="BG1" s="51"/>
+      <c r="BH1" s="51"/>
+      <c r="BI1" s="51"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1579,82 +1558,82 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="42" t="s">
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="42" t="s">
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="41" t="str">
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="50" t="str">
         <f>G5</f>
         <v>ItemSerchService</v>
       </c>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="41"/>
-      <c r="AM2" s="41"/>
-      <c r="AN2" s="41"/>
-      <c r="AO2" s="41"/>
-      <c r="AP2" s="41"/>
-      <c r="AQ2" s="42" t="s">
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AR2" s="42"/>
-      <c r="AS2" s="42"/>
-      <c r="AT2" s="41" t="s">
+      <c r="AR2" s="49"/>
+      <c r="AS2" s="49"/>
+      <c r="AT2" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AU2" s="41"/>
-      <c r="AV2" s="41"/>
-      <c r="AW2" s="41"/>
-      <c r="AX2" s="41"/>
-      <c r="AY2" s="41"/>
-      <c r="AZ2" s="41"/>
-      <c r="BA2" s="42" t="s">
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="50"/>
+      <c r="BA2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="BB2" s="42"/>
-      <c r="BC2" s="42"/>
-      <c r="BD2" s="39">
+      <c r="BB2" s="49"/>
+      <c r="BC2" s="49"/>
+      <c r="BD2" s="51">
         <v>45553</v>
       </c>
-      <c r="BE2" s="39"/>
-      <c r="BF2" s="39"/>
-      <c r="BG2" s="39"/>
-      <c r="BH2" s="39"/>
-      <c r="BI2" s="39"/>
+      <c r="BE2" s="51"/>
+      <c r="BF2" s="51"/>
+      <c r="BG2" s="51"/>
+      <c r="BH2" s="51"/>
+      <c r="BI2" s="51"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1917,927 +1896,942 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38" t="s">
-        <v>80</v>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53" t="s">
+        <v>76</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="53"/>
+      <c r="U4" s="53"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="53"/>
+      <c r="X4" s="53"/>
+      <c r="Y4" s="53"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="53"/>
+      <c r="AB4" s="53"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="53"/>
+      <c r="AE4" s="53"/>
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="53"/>
+      <c r="AH4" s="53"/>
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="53"/>
+      <c r="AK4" s="53"/>
+      <c r="AL4" s="53"/>
+      <c r="AM4" s="53"/>
+      <c r="AN4" s="53"/>
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="53"/>
+      <c r="AQ4" s="53"/>
+      <c r="AR4" s="53"/>
+      <c r="AS4" s="53"/>
+      <c r="AT4" s="53"/>
+      <c r="AU4" s="53"/>
+      <c r="AV4" s="53"/>
+      <c r="AW4" s="53"/>
+      <c r="AX4" s="53"/>
+      <c r="AY4" s="53"/>
+      <c r="AZ4" s="53"/>
+      <c r="BA4" s="53"/>
+      <c r="BB4" s="53"/>
+      <c r="BC4" s="53"/>
+      <c r="BD4" s="53"/>
+      <c r="BE4" s="53"/>
+      <c r="BF4" s="53"/>
+      <c r="BG4" s="53"/>
+      <c r="BH4" s="53"/>
+      <c r="BI4" s="53"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38" t="s">
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="53"/>
+      <c r="U5" s="53"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="53"/>
+      <c r="AB5" s="53"/>
+      <c r="AC5" s="53"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="53"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
+      <c r="AM5" s="53"/>
+      <c r="AN5" s="53"/>
+      <c r="AO5" s="53"/>
+      <c r="AP5" s="53"/>
+      <c r="AQ5" s="53"/>
+      <c r="AR5" s="53"/>
+      <c r="AS5" s="53"/>
+      <c r="AT5" s="53"/>
+      <c r="AU5" s="53"/>
+      <c r="AV5" s="53"/>
+      <c r="AW5" s="53"/>
+      <c r="AX5" s="53"/>
+      <c r="AY5" s="53"/>
+      <c r="AZ5" s="53"/>
+      <c r="BA5" s="53"/>
+      <c r="BB5" s="53"/>
+      <c r="BC5" s="53"/>
+      <c r="BD5" s="53"/>
+      <c r="BE5" s="53"/>
+      <c r="BF5" s="53"/>
+      <c r="BG5" s="53"/>
+      <c r="BH5" s="53"/>
+      <c r="BI5" s="53"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38" t="s">
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="38"/>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="38"/>
-      <c r="AC6" s="38"/>
-      <c r="AD6" s="37" t="s">
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="53"/>
+      <c r="P6" s="53"/>
+      <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="53"/>
+      <c r="U6" s="53"/>
+      <c r="V6" s="53"/>
+      <c r="W6" s="53"/>
+      <c r="X6" s="53"/>
+      <c r="Y6" s="53"/>
+      <c r="Z6" s="53"/>
+      <c r="AA6" s="53"/>
+      <c r="AB6" s="53"/>
+      <c r="AC6" s="53"/>
+      <c r="AD6" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="37"/>
-      <c r="AG6" s="37"/>
-      <c r="AH6" s="37"/>
-      <c r="AI6" s="37"/>
-      <c r="AJ6" s="38" t="s">
+      <c r="AE6" s="52"/>
+      <c r="AF6" s="52"/>
+      <c r="AG6" s="52"/>
+      <c r="AH6" s="52"/>
+      <c r="AI6" s="52"/>
+      <c r="AJ6" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="AK6" s="38"/>
-      <c r="AL6" s="38"/>
-      <c r="AM6" s="38"/>
-      <c r="AN6" s="38"/>
-      <c r="AO6" s="38"/>
-      <c r="AP6" s="38"/>
-      <c r="AQ6" s="38"/>
-      <c r="AR6" s="38"/>
-      <c r="AS6" s="38"/>
-      <c r="AT6" s="38"/>
-      <c r="AU6" s="38"/>
-      <c r="AV6" s="38"/>
-      <c r="AW6" s="38"/>
-      <c r="AX6" s="38"/>
-      <c r="AY6" s="38"/>
-      <c r="AZ6" s="38"/>
-      <c r="BA6" s="38"/>
-      <c r="BB6" s="38"/>
-      <c r="BC6" s="38"/>
-      <c r="BD6" s="38"/>
-      <c r="BE6" s="38"/>
-      <c r="BF6" s="38"/>
-      <c r="BG6" s="38"/>
-      <c r="BH6" s="38"/>
-      <c r="BI6" s="38"/>
+      <c r="AK6" s="53"/>
+      <c r="AL6" s="53"/>
+      <c r="AM6" s="53"/>
+      <c r="AN6" s="53"/>
+      <c r="AO6" s="53"/>
+      <c r="AP6" s="53"/>
+      <c r="AQ6" s="53"/>
+      <c r="AR6" s="53"/>
+      <c r="AS6" s="53"/>
+      <c r="AT6" s="53"/>
+      <c r="AU6" s="53"/>
+      <c r="AV6" s="53"/>
+      <c r="AW6" s="53"/>
+      <c r="AX6" s="53"/>
+      <c r="AY6" s="53"/>
+      <c r="AZ6" s="53"/>
+      <c r="BA6" s="53"/>
+      <c r="BB6" s="53"/>
+      <c r="BC6" s="53"/>
+      <c r="BD6" s="53"/>
+      <c r="BE6" s="53"/>
+      <c r="BF6" s="53"/>
+      <c r="BG6" s="53"/>
+      <c r="BH6" s="53"/>
+      <c r="BI6" s="53"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37" t="s">
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37" t="s">
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="52"/>
+      <c r="Q8" s="52"/>
+      <c r="R8" s="52"/>
+      <c r="S8" s="52"/>
+      <c r="T8" s="52"/>
+      <c r="U8" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37" t="s">
+      <c r="V8" s="52"/>
+      <c r="W8" s="52"/>
+      <c r="X8" s="52"/>
+      <c r="Y8" s="52"/>
+      <c r="Z8" s="52"/>
+      <c r="AA8" s="52"/>
+      <c r="AB8" s="52"/>
+      <c r="AC8" s="52"/>
+      <c r="AD8" s="52"/>
+      <c r="AE8" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="AF8" s="37"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="37"/>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="37"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="37" t="s">
+      <c r="AF8" s="52"/>
+      <c r="AG8" s="52"/>
+      <c r="AH8" s="52"/>
+      <c r="AI8" s="52"/>
+      <c r="AJ8" s="52"/>
+      <c r="AK8" s="52"/>
+      <c r="AL8" s="52"/>
+      <c r="AM8" s="52"/>
+      <c r="AN8" s="52"/>
+      <c r="AO8" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="AP8" s="37"/>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="37"/>
-      <c r="AS8" s="37"/>
-      <c r="AT8" s="37"/>
-      <c r="AU8" s="37"/>
-      <c r="AV8" s="37"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="37"/>
-      <c r="AY8" s="37"/>
-      <c r="AZ8" s="37"/>
-      <c r="BA8" s="37"/>
-      <c r="BB8" s="37"/>
-      <c r="BC8" s="37"/>
-      <c r="BD8" s="37"/>
-      <c r="BE8" s="37"/>
-      <c r="BF8" s="37"/>
-      <c r="BG8" s="37"/>
-      <c r="BH8" s="37"/>
-      <c r="BI8" s="37"/>
+      <c r="AP8" s="52"/>
+      <c r="AQ8" s="52"/>
+      <c r="AR8" s="52"/>
+      <c r="AS8" s="52"/>
+      <c r="AT8" s="52"/>
+      <c r="AU8" s="52"/>
+      <c r="AV8" s="52"/>
+      <c r="AW8" s="52"/>
+      <c r="AX8" s="52"/>
+      <c r="AY8" s="52"/>
+      <c r="AZ8" s="52"/>
+      <c r="BA8" s="52"/>
+      <c r="BB8" s="52"/>
+      <c r="BC8" s="52"/>
+      <c r="BD8" s="52"/>
+      <c r="BE8" s="52"/>
+      <c r="BF8" s="52"/>
+      <c r="BG8" s="52"/>
+      <c r="BH8" s="52"/>
+      <c r="BI8" s="52"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="36"/>
-      <c r="AD9" s="36"/>
-      <c r="AE9" s="36"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="36"/>
-      <c r="AH9" s="36"/>
-      <c r="AI9" s="36"/>
-      <c r="AJ9" s="36"/>
-      <c r="AK9" s="36"/>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="36"/>
-      <c r="AN9" s="36"/>
-      <c r="AO9" s="36"/>
-      <c r="AP9" s="36"/>
-      <c r="AQ9" s="36"/>
-      <c r="AR9" s="36"/>
-      <c r="AS9" s="36"/>
-      <c r="AT9" s="36"/>
-      <c r="AU9" s="36"/>
-      <c r="AV9" s="36"/>
-      <c r="AW9" s="36"/>
-      <c r="AX9" s="36"/>
-      <c r="AY9" s="36"/>
-      <c r="AZ9" s="36"/>
-      <c r="BA9" s="36"/>
-      <c r="BB9" s="36"/>
-      <c r="BC9" s="36"/>
-      <c r="BD9" s="36"/>
-      <c r="BE9" s="36"/>
-      <c r="BF9" s="36"/>
-      <c r="BG9" s="36"/>
-      <c r="BH9" s="36"/>
-      <c r="BI9" s="36"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="56"/>
+      <c r="Q9" s="56"/>
+      <c r="R9" s="56"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="56"/>
+      <c r="U9" s="56"/>
+      <c r="V9" s="56"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="56"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="56"/>
+      <c r="AA9" s="56"/>
+      <c r="AB9" s="56"/>
+      <c r="AC9" s="56"/>
+      <c r="AD9" s="56"/>
+      <c r="AE9" s="56"/>
+      <c r="AF9" s="56"/>
+      <c r="AG9" s="56"/>
+      <c r="AH9" s="56"/>
+      <c r="AI9" s="56"/>
+      <c r="AJ9" s="56"/>
+      <c r="AK9" s="56"/>
+      <c r="AL9" s="56"/>
+      <c r="AM9" s="56"/>
+      <c r="AN9" s="56"/>
+      <c r="AO9" s="56"/>
+      <c r="AP9" s="56"/>
+      <c r="AQ9" s="56"/>
+      <c r="AR9" s="56"/>
+      <c r="AS9" s="56"/>
+      <c r="AT9" s="56"/>
+      <c r="AU9" s="56"/>
+      <c r="AV9" s="56"/>
+      <c r="AW9" s="56"/>
+      <c r="AX9" s="56"/>
+      <c r="AY9" s="56"/>
+      <c r="AZ9" s="56"/>
+      <c r="BA9" s="56"/>
+      <c r="BB9" s="56"/>
+      <c r="BC9" s="56"/>
+      <c r="BD9" s="56"/>
+      <c r="BE9" s="56"/>
+      <c r="BF9" s="56"/>
+      <c r="BG9" s="56"/>
+      <c r="BH9" s="56"/>
+      <c r="BI9" s="56"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="36"/>
-      <c r="AB10" s="36"/>
-      <c r="AC10" s="36"/>
-      <c r="AD10" s="36"/>
-      <c r="AE10" s="36"/>
-      <c r="AF10" s="36"/>
-      <c r="AG10" s="36"/>
-      <c r="AH10" s="36"/>
-      <c r="AI10" s="36"/>
-      <c r="AJ10" s="36"/>
-      <c r="AK10" s="36"/>
-      <c r="AL10" s="36"/>
-      <c r="AM10" s="36"/>
-      <c r="AN10" s="36"/>
-      <c r="AO10" s="36"/>
-      <c r="AP10" s="36"/>
-      <c r="AQ10" s="36"/>
-      <c r="AR10" s="36"/>
-      <c r="AS10" s="36"/>
-      <c r="AT10" s="36"/>
-      <c r="AU10" s="36"/>
-      <c r="AV10" s="36"/>
-      <c r="AW10" s="36"/>
-      <c r="AX10" s="36"/>
-      <c r="AY10" s="36"/>
-      <c r="AZ10" s="36"/>
-      <c r="BA10" s="36"/>
-      <c r="BB10" s="36"/>
-      <c r="BC10" s="36"/>
-      <c r="BD10" s="36"/>
-      <c r="BE10" s="36"/>
-      <c r="BF10" s="36"/>
-      <c r="BG10" s="36"/>
-      <c r="BH10" s="36"/>
-      <c r="BI10" s="36"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="56"/>
+      <c r="V10" s="56"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="56"/>
+      <c r="Z10" s="56"/>
+      <c r="AA10" s="56"/>
+      <c r="AB10" s="56"/>
+      <c r="AC10" s="56"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="56"/>
+      <c r="AH10" s="56"/>
+      <c r="AI10" s="56"/>
+      <c r="AJ10" s="56"/>
+      <c r="AK10" s="56"/>
+      <c r="AL10" s="56"/>
+      <c r="AM10" s="56"/>
+      <c r="AN10" s="56"/>
+      <c r="AO10" s="56"/>
+      <c r="AP10" s="56"/>
+      <c r="AQ10" s="56"/>
+      <c r="AR10" s="56"/>
+      <c r="AS10" s="56"/>
+      <c r="AT10" s="56"/>
+      <c r="AU10" s="56"/>
+      <c r="AV10" s="56"/>
+      <c r="AW10" s="56"/>
+      <c r="AX10" s="56"/>
+      <c r="AY10" s="56"/>
+      <c r="AZ10" s="56"/>
+      <c r="BA10" s="56"/>
+      <c r="BB10" s="56"/>
+      <c r="BC10" s="56"/>
+      <c r="BD10" s="56"/>
+      <c r="BE10" s="56"/>
+      <c r="BF10" s="56"/>
+      <c r="BG10" s="56"/>
+      <c r="BH10" s="56"/>
+      <c r="BI10" s="56"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="36"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="36"/>
-      <c r="AD11" s="36"/>
-      <c r="AE11" s="36"/>
-      <c r="AF11" s="36"/>
-      <c r="AG11" s="36"/>
-      <c r="AH11" s="36"/>
-      <c r="AI11" s="36"/>
-      <c r="AJ11" s="36"/>
-      <c r="AK11" s="36"/>
-      <c r="AL11" s="36"/>
-      <c r="AM11" s="36"/>
-      <c r="AN11" s="36"/>
-      <c r="AO11" s="36"/>
-      <c r="AP11" s="36"/>
-      <c r="AQ11" s="36"/>
-      <c r="AR11" s="36"/>
-      <c r="AS11" s="36"/>
-      <c r="AT11" s="36"/>
-      <c r="AU11" s="36"/>
-      <c r="AV11" s="36"/>
-      <c r="AW11" s="36"/>
-      <c r="AX11" s="36"/>
-      <c r="AY11" s="36"/>
-      <c r="AZ11" s="36"/>
-      <c r="BA11" s="36"/>
-      <c r="BB11" s="36"/>
-      <c r="BC11" s="36"/>
-      <c r="BD11" s="36"/>
-      <c r="BE11" s="36"/>
-      <c r="BF11" s="36"/>
-      <c r="BG11" s="36"/>
-      <c r="BH11" s="36"/>
-      <c r="BI11" s="36"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56"/>
+      <c r="Q11" s="56"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="56"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="56"/>
+      <c r="Z11" s="56"/>
+      <c r="AA11" s="56"/>
+      <c r="AB11" s="56"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="56"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="56"/>
+      <c r="AH11" s="56"/>
+      <c r="AI11" s="56"/>
+      <c r="AJ11" s="56"/>
+      <c r="AK11" s="56"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="56"/>
+      <c r="AN11" s="56"/>
+      <c r="AO11" s="56"/>
+      <c r="AP11" s="56"/>
+      <c r="AQ11" s="56"/>
+      <c r="AR11" s="56"/>
+      <c r="AS11" s="56"/>
+      <c r="AT11" s="56"/>
+      <c r="AU11" s="56"/>
+      <c r="AV11" s="56"/>
+      <c r="AW11" s="56"/>
+      <c r="AX11" s="56"/>
+      <c r="AY11" s="56"/>
+      <c r="AZ11" s="56"/>
+      <c r="BA11" s="56"/>
+      <c r="BB11" s="56"/>
+      <c r="BC11" s="56"/>
+      <c r="BD11" s="56"/>
+      <c r="BE11" s="56"/>
+      <c r="BF11" s="56"/>
+      <c r="BG11" s="56"/>
+      <c r="BH11" s="56"/>
+      <c r="BI11" s="56"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="37"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="37"/>
-      <c r="AD13" s="37"/>
-      <c r="AE13" s="37"/>
-      <c r="AF13" s="37"/>
-      <c r="AG13" s="37"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="37"/>
-      <c r="AJ13" s="37"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="37"/>
-      <c r="AM13" s="37"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="37"/>
-      <c r="AP13" s="37"/>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="37"/>
-      <c r="AS13" s="37"/>
-      <c r="AT13" s="37"/>
-      <c r="AU13" s="37"/>
-      <c r="AV13" s="37"/>
-      <c r="AW13" s="37"/>
-      <c r="AX13" s="37"/>
-      <c r="AY13" s="37"/>
-      <c r="AZ13" s="37"/>
-      <c r="BA13" s="37"/>
-      <c r="BB13" s="37"/>
-      <c r="BC13" s="37"/>
-      <c r="BD13" s="37"/>
-      <c r="BE13" s="37"/>
-      <c r="BF13" s="37"/>
-      <c r="BG13" s="37"/>
-      <c r="BH13" s="37"/>
-      <c r="BI13" s="37"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
+      <c r="P13" s="52"/>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="52"/>
+      <c r="V13" s="52"/>
+      <c r="W13" s="52"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="52"/>
+      <c r="AA13" s="52"/>
+      <c r="AB13" s="52"/>
+      <c r="AC13" s="52"/>
+      <c r="AD13" s="52"/>
+      <c r="AE13" s="52"/>
+      <c r="AF13" s="52"/>
+      <c r="AG13" s="52"/>
+      <c r="AH13" s="52"/>
+      <c r="AI13" s="52"/>
+      <c r="AJ13" s="52"/>
+      <c r="AK13" s="52"/>
+      <c r="AL13" s="52"/>
+      <c r="AM13" s="52"/>
+      <c r="AN13" s="52"/>
+      <c r="AO13" s="52"/>
+      <c r="AP13" s="52"/>
+      <c r="AQ13" s="52"/>
+      <c r="AR13" s="52"/>
+      <c r="AS13" s="52"/>
+      <c r="AT13" s="52"/>
+      <c r="AU13" s="52"/>
+      <c r="AV13" s="52"/>
+      <c r="AW13" s="52"/>
+      <c r="AX13" s="52"/>
+      <c r="AY13" s="52"/>
+      <c r="AZ13" s="52"/>
+      <c r="BA13" s="52"/>
+      <c r="BB13" s="52"/>
+      <c r="BC13" s="52"/>
+      <c r="BD13" s="52"/>
+      <c r="BE13" s="52"/>
+      <c r="BF13" s="52"/>
+      <c r="BG13" s="52"/>
+      <c r="BH13" s="52"/>
+      <c r="BI13" s="52"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="36"/>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="36"/>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="36"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="36"/>
-      <c r="AD14" s="36"/>
-      <c r="AE14" s="36"/>
-      <c r="AF14" s="36"/>
-      <c r="AG14" s="36"/>
-      <c r="AH14" s="36"/>
-      <c r="AI14" s="36"/>
-      <c r="AJ14" s="36"/>
-      <c r="AK14" s="36"/>
-      <c r="AL14" s="36"/>
-      <c r="AM14" s="36"/>
-      <c r="AN14" s="36"/>
-      <c r="AO14" s="36"/>
-      <c r="AP14" s="36"/>
-      <c r="AQ14" s="36"/>
-      <c r="AR14" s="36"/>
-      <c r="AS14" s="36"/>
-      <c r="AT14" s="36"/>
-      <c r="AU14" s="36"/>
-      <c r="AV14" s="36"/>
-      <c r="AW14" s="36"/>
-      <c r="AX14" s="36"/>
-      <c r="AY14" s="36"/>
-      <c r="AZ14" s="36"/>
-      <c r="BA14" s="36"/>
-      <c r="BB14" s="36"/>
-      <c r="BC14" s="36"/>
-      <c r="BD14" s="36"/>
-      <c r="BE14" s="36"/>
-      <c r="BF14" s="36"/>
-      <c r="BG14" s="36"/>
-      <c r="BH14" s="36"/>
-      <c r="BI14" s="36"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="56"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="56"/>
+      <c r="V14" s="56"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="56"/>
+      <c r="Y14" s="56"/>
+      <c r="Z14" s="56"/>
+      <c r="AA14" s="56"/>
+      <c r="AB14" s="56"/>
+      <c r="AC14" s="56"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="56"/>
+      <c r="AG14" s="56"/>
+      <c r="AH14" s="56"/>
+      <c r="AI14" s="56"/>
+      <c r="AJ14" s="56"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="56"/>
+      <c r="AM14" s="56"/>
+      <c r="AN14" s="56"/>
+      <c r="AO14" s="56"/>
+      <c r="AP14" s="56"/>
+      <c r="AQ14" s="56"/>
+      <c r="AR14" s="56"/>
+      <c r="AS14" s="56"/>
+      <c r="AT14" s="56"/>
+      <c r="AU14" s="56"/>
+      <c r="AV14" s="56"/>
+      <c r="AW14" s="56"/>
+      <c r="AX14" s="56"/>
+      <c r="AY14" s="56"/>
+      <c r="AZ14" s="56"/>
+      <c r="BA14" s="56"/>
+      <c r="BB14" s="56"/>
+      <c r="BC14" s="56"/>
+      <c r="BD14" s="56"/>
+      <c r="BE14" s="56"/>
+      <c r="BF14" s="56"/>
+      <c r="BG14" s="56"/>
+      <c r="BH14" s="56"/>
+      <c r="BI14" s="56"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
-      <c r="S15" s="36"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="36"/>
-      <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="36"/>
-      <c r="Y15" s="36"/>
-      <c r="Z15" s="36"/>
-      <c r="AA15" s="36"/>
-      <c r="AB15" s="36"/>
-      <c r="AC15" s="36"/>
-      <c r="AD15" s="36"/>
-      <c r="AE15" s="36"/>
-      <c r="AF15" s="36"/>
-      <c r="AG15" s="36"/>
-      <c r="AH15" s="36"/>
-      <c r="AI15" s="36"/>
-      <c r="AJ15" s="36"/>
-      <c r="AK15" s="36"/>
-      <c r="AL15" s="36"/>
-      <c r="AM15" s="36"/>
-      <c r="AN15" s="36"/>
-      <c r="AO15" s="36"/>
-      <c r="AP15" s="36"/>
-      <c r="AQ15" s="36"/>
-      <c r="AR15" s="36"/>
-      <c r="AS15" s="36"/>
-      <c r="AT15" s="36"/>
-      <c r="AU15" s="36"/>
-      <c r="AV15" s="36"/>
-      <c r="AW15" s="36"/>
-      <c r="AX15" s="36"/>
-      <c r="AY15" s="36"/>
-      <c r="AZ15" s="36"/>
-      <c r="BA15" s="36"/>
-      <c r="BB15" s="36"/>
-      <c r="BC15" s="36"/>
-      <c r="BD15" s="36"/>
-      <c r="BE15" s="36"/>
-      <c r="BF15" s="36"/>
-      <c r="BG15" s="36"/>
-      <c r="BH15" s="36"/>
-      <c r="BI15" s="36"/>
+      <c r="A15" s="56"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="56"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="56"/>
+      <c r="U15" s="56"/>
+      <c r="V15" s="56"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="56"/>
+      <c r="Z15" s="56"/>
+      <c r="AA15" s="56"/>
+      <c r="AB15" s="56"/>
+      <c r="AC15" s="56"/>
+      <c r="AD15" s="56"/>
+      <c r="AE15" s="56"/>
+      <c r="AF15" s="56"/>
+      <c r="AG15" s="56"/>
+      <c r="AH15" s="56"/>
+      <c r="AI15" s="56"/>
+      <c r="AJ15" s="56"/>
+      <c r="AK15" s="56"/>
+      <c r="AL15" s="56"/>
+      <c r="AM15" s="56"/>
+      <c r="AN15" s="56"/>
+      <c r="AO15" s="56"/>
+      <c r="AP15" s="56"/>
+      <c r="AQ15" s="56"/>
+      <c r="AR15" s="56"/>
+      <c r="AS15" s="56"/>
+      <c r="AT15" s="56"/>
+      <c r="AU15" s="56"/>
+      <c r="AV15" s="56"/>
+      <c r="AW15" s="56"/>
+      <c r="AX15" s="56"/>
+      <c r="AY15" s="56"/>
+      <c r="AZ15" s="56"/>
+      <c r="BA15" s="56"/>
+      <c r="BB15" s="56"/>
+      <c r="BC15" s="56"/>
+      <c r="BD15" s="56"/>
+      <c r="BE15" s="56"/>
+      <c r="BF15" s="56"/>
+      <c r="BG15" s="56"/>
+      <c r="BH15" s="56"/>
+      <c r="BI15" s="56"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="36"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="36"/>
-      <c r="AD16" s="36"/>
-      <c r="AE16" s="36"/>
-      <c r="AF16" s="36"/>
-      <c r="AG16" s="36"/>
-      <c r="AH16" s="36"/>
-      <c r="AI16" s="36"/>
-      <c r="AJ16" s="36"/>
-      <c r="AK16" s="36"/>
-      <c r="AL16" s="36"/>
-      <c r="AM16" s="36"/>
-      <c r="AN16" s="36"/>
-      <c r="AO16" s="36"/>
-      <c r="AP16" s="36"/>
-      <c r="AQ16" s="36"/>
-      <c r="AR16" s="36"/>
-      <c r="AS16" s="36"/>
-      <c r="AT16" s="36"/>
-      <c r="AU16" s="36"/>
-      <c r="AV16" s="36"/>
-      <c r="AW16" s="36"/>
-      <c r="AX16" s="36"/>
-      <c r="AY16" s="36"/>
-      <c r="AZ16" s="36"/>
-      <c r="BA16" s="36"/>
-      <c r="BB16" s="36"/>
-      <c r="BC16" s="36"/>
-      <c r="BD16" s="36"/>
-      <c r="BE16" s="36"/>
-      <c r="BF16" s="36"/>
-      <c r="BG16" s="36"/>
-      <c r="BH16" s="36"/>
-      <c r="BI16" s="36"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="56"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="56"/>
+      <c r="U16" s="56"/>
+      <c r="V16" s="56"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="56"/>
+      <c r="Y16" s="56"/>
+      <c r="Z16" s="56"/>
+      <c r="AA16" s="56"/>
+      <c r="AB16" s="56"/>
+      <c r="AC16" s="56"/>
+      <c r="AD16" s="56"/>
+      <c r="AE16" s="56"/>
+      <c r="AF16" s="56"/>
+      <c r="AG16" s="56"/>
+      <c r="AH16" s="56"/>
+      <c r="AI16" s="56"/>
+      <c r="AJ16" s="56"/>
+      <c r="AK16" s="56"/>
+      <c r="AL16" s="56"/>
+      <c r="AM16" s="56"/>
+      <c r="AN16" s="56"/>
+      <c r="AO16" s="56"/>
+      <c r="AP16" s="56"/>
+      <c r="AQ16" s="56"/>
+      <c r="AR16" s="56"/>
+      <c r="AS16" s="56"/>
+      <c r="AT16" s="56"/>
+      <c r="AU16" s="56"/>
+      <c r="AV16" s="56"/>
+      <c r="AW16" s="56"/>
+      <c r="AX16" s="56"/>
+      <c r="AY16" s="56"/>
+      <c r="AZ16" s="56"/>
+      <c r="BA16" s="56"/>
+      <c r="BB16" s="56"/>
+      <c r="BC16" s="56"/>
+      <c r="BD16" s="56"/>
+      <c r="BE16" s="56"/>
+      <c r="BF16" s="56"/>
+      <c r="BG16" s="56"/>
+      <c r="BH16" s="56"/>
+      <c r="BI16" s="56"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="36"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="36"/>
-      <c r="AB17" s="36"/>
-      <c r="AC17" s="36"/>
-      <c r="AD17" s="36"/>
-      <c r="AE17" s="36"/>
-      <c r="AF17" s="36"/>
-      <c r="AG17" s="36"/>
-      <c r="AH17" s="36"/>
-      <c r="AI17" s="36"/>
-      <c r="AJ17" s="36"/>
-      <c r="AK17" s="36"/>
-      <c r="AL17" s="36"/>
-      <c r="AM17" s="36"/>
-      <c r="AN17" s="36"/>
-      <c r="AO17" s="36"/>
-      <c r="AP17" s="36"/>
-      <c r="AQ17" s="36"/>
-      <c r="AR17" s="36"/>
-      <c r="AS17" s="36"/>
-      <c r="AT17" s="36"/>
-      <c r="AU17" s="36"/>
-      <c r="AV17" s="36"/>
-      <c r="AW17" s="36"/>
-      <c r="AX17" s="36"/>
-      <c r="AY17" s="36"/>
-      <c r="AZ17" s="36"/>
-      <c r="BA17" s="36"/>
-      <c r="BB17" s="36"/>
-      <c r="BC17" s="36"/>
-      <c r="BD17" s="36"/>
-      <c r="BE17" s="36"/>
-      <c r="BF17" s="36"/>
-      <c r="BG17" s="36"/>
-      <c r="BH17" s="36"/>
-      <c r="BI17" s="36"/>
+      <c r="A17" s="56"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="56"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="56"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="56"/>
+      <c r="U17" s="56"/>
+      <c r="V17" s="56"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="56"/>
+      <c r="Y17" s="56"/>
+      <c r="Z17" s="56"/>
+      <c r="AA17" s="56"/>
+      <c r="AB17" s="56"/>
+      <c r="AC17" s="56"/>
+      <c r="AD17" s="56"/>
+      <c r="AE17" s="56"/>
+      <c r="AF17" s="56"/>
+      <c r="AG17" s="56"/>
+      <c r="AH17" s="56"/>
+      <c r="AI17" s="56"/>
+      <c r="AJ17" s="56"/>
+      <c r="AK17" s="56"/>
+      <c r="AL17" s="56"/>
+      <c r="AM17" s="56"/>
+      <c r="AN17" s="56"/>
+      <c r="AO17" s="56"/>
+      <c r="AP17" s="56"/>
+      <c r="AQ17" s="56"/>
+      <c r="AR17" s="56"/>
+      <c r="AS17" s="56"/>
+      <c r="AT17" s="56"/>
+      <c r="AU17" s="56"/>
+      <c r="AV17" s="56"/>
+      <c r="AW17" s="56"/>
+      <c r="AX17" s="56"/>
+      <c r="AY17" s="56"/>
+      <c r="AZ17" s="56"/>
+      <c r="BA17" s="56"/>
+      <c r="BB17" s="56"/>
+      <c r="BC17" s="56"/>
+      <c r="BD17" s="56"/>
+      <c r="BE17" s="56"/>
+      <c r="BF17" s="56"/>
+      <c r="BG17" s="56"/>
+      <c r="BH17" s="56"/>
+      <c r="BI17" s="56"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="36"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="36"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="36"/>
-      <c r="AC18" s="36"/>
-      <c r="AD18" s="36"/>
-      <c r="AE18" s="36"/>
-      <c r="AF18" s="36"/>
-      <c r="AG18" s="36"/>
-      <c r="AH18" s="36"/>
-      <c r="AI18" s="36"/>
-      <c r="AJ18" s="36"/>
-      <c r="AK18" s="36"/>
-      <c r="AL18" s="36"/>
-      <c r="AM18" s="36"/>
-      <c r="AN18" s="36"/>
-      <c r="AO18" s="36"/>
-      <c r="AP18" s="36"/>
-      <c r="AQ18" s="36"/>
-      <c r="AR18" s="36"/>
-      <c r="AS18" s="36"/>
-      <c r="AT18" s="36"/>
-      <c r="AU18" s="36"/>
-      <c r="AV18" s="36"/>
-      <c r="AW18" s="36"/>
-      <c r="AX18" s="36"/>
-      <c r="AY18" s="36"/>
-      <c r="AZ18" s="36"/>
-      <c r="BA18" s="36"/>
-      <c r="BB18" s="36"/>
-      <c r="BC18" s="36"/>
-      <c r="BD18" s="36"/>
-      <c r="BE18" s="36"/>
-      <c r="BF18" s="36"/>
-      <c r="BG18" s="36"/>
-      <c r="BH18" s="36"/>
-      <c r="BI18" s="36"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="56"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="56"/>
+      <c r="R18" s="56"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="56"/>
+      <c r="U18" s="56"/>
+      <c r="V18" s="56"/>
+      <c r="W18" s="56"/>
+      <c r="X18" s="56"/>
+      <c r="Y18" s="56"/>
+      <c r="Z18" s="56"/>
+      <c r="AA18" s="56"/>
+      <c r="AB18" s="56"/>
+      <c r="AC18" s="56"/>
+      <c r="AD18" s="56"/>
+      <c r="AE18" s="56"/>
+      <c r="AF18" s="56"/>
+      <c r="AG18" s="56"/>
+      <c r="AH18" s="56"/>
+      <c r="AI18" s="56"/>
+      <c r="AJ18" s="56"/>
+      <c r="AK18" s="56"/>
+      <c r="AL18" s="56"/>
+      <c r="AM18" s="56"/>
+      <c r="AN18" s="56"/>
+      <c r="AO18" s="56"/>
+      <c r="AP18" s="56"/>
+      <c r="AQ18" s="56"/>
+      <c r="AR18" s="56"/>
+      <c r="AS18" s="56"/>
+      <c r="AT18" s="56"/>
+      <c r="AU18" s="56"/>
+      <c r="AV18" s="56"/>
+      <c r="AW18" s="56"/>
+      <c r="AX18" s="56"/>
+      <c r="AY18" s="56"/>
+      <c r="AZ18" s="56"/>
+      <c r="BA18" s="56"/>
+      <c r="BB18" s="56"/>
+      <c r="BC18" s="56"/>
+      <c r="BD18" s="56"/>
+      <c r="BE18" s="56"/>
+      <c r="BF18" s="56"/>
+      <c r="BG18" s="56"/>
+      <c r="BH18" s="56"/>
+      <c r="BI18" s="56"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="36"/>
-      <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="36"/>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="36"/>
-      <c r="AA19" s="36"/>
-      <c r="AB19" s="36"/>
-      <c r="AC19" s="36"/>
-      <c r="AD19" s="36"/>
-      <c r="AE19" s="36"/>
-      <c r="AF19" s="36"/>
-      <c r="AG19" s="36"/>
-      <c r="AH19" s="36"/>
-      <c r="AI19" s="36"/>
-      <c r="AJ19" s="36"/>
-      <c r="AK19" s="36"/>
-      <c r="AL19" s="36"/>
-      <c r="AM19" s="36"/>
-      <c r="AN19" s="36"/>
-      <c r="AO19" s="36"/>
-      <c r="AP19" s="36"/>
-      <c r="AQ19" s="36"/>
-      <c r="AR19" s="36"/>
-      <c r="AS19" s="36"/>
-      <c r="AT19" s="36"/>
-      <c r="AU19" s="36"/>
-      <c r="AV19" s="36"/>
-      <c r="AW19" s="36"/>
-      <c r="AX19" s="36"/>
-      <c r="AY19" s="36"/>
-      <c r="AZ19" s="36"/>
-      <c r="BA19" s="36"/>
-      <c r="BB19" s="36"/>
-      <c r="BC19" s="36"/>
-      <c r="BD19" s="36"/>
-      <c r="BE19" s="36"/>
-      <c r="BF19" s="36"/>
-      <c r="BG19" s="36"/>
-      <c r="BH19" s="36"/>
-      <c r="BI19" s="36"/>
+      <c r="A19" s="56"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="56"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="56"/>
+      <c r="P19" s="56"/>
+      <c r="Q19" s="56"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="56"/>
+      <c r="U19" s="56"/>
+      <c r="V19" s="56"/>
+      <c r="W19" s="56"/>
+      <c r="X19" s="56"/>
+      <c r="Y19" s="56"/>
+      <c r="Z19" s="56"/>
+      <c r="AA19" s="56"/>
+      <c r="AB19" s="56"/>
+      <c r="AC19" s="56"/>
+      <c r="AD19" s="56"/>
+      <c r="AE19" s="56"/>
+      <c r="AF19" s="56"/>
+      <c r="AG19" s="56"/>
+      <c r="AH19" s="56"/>
+      <c r="AI19" s="56"/>
+      <c r="AJ19" s="56"/>
+      <c r="AK19" s="56"/>
+      <c r="AL19" s="56"/>
+      <c r="AM19" s="56"/>
+      <c r="AN19" s="56"/>
+      <c r="AO19" s="56"/>
+      <c r="AP19" s="56"/>
+      <c r="AQ19" s="56"/>
+      <c r="AR19" s="56"/>
+      <c r="AS19" s="56"/>
+      <c r="AT19" s="56"/>
+      <c r="AU19" s="56"/>
+      <c r="AV19" s="56"/>
+      <c r="AW19" s="56"/>
+      <c r="AX19" s="56"/>
+      <c r="AY19" s="56"/>
+      <c r="AZ19" s="56"/>
+      <c r="BA19" s="56"/>
+      <c r="BB19" s="56"/>
+      <c r="BC19" s="56"/>
+      <c r="BD19" s="56"/>
+      <c r="BE19" s="56"/>
+      <c r="BF19" s="56"/>
+      <c r="BG19" s="56"/>
+      <c r="BH19" s="56"/>
+      <c r="BI19" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="A14:BI19"/>
+    <mergeCell ref="A13:BI13"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="U10:AD10"/>
+    <mergeCell ref="AE10:AN10"/>
+    <mergeCell ref="AO10:BI10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="U11:AD11"/>
+    <mergeCell ref="AE11:AN11"/>
+    <mergeCell ref="AO11:BI11"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="U8:AD8"/>
+    <mergeCell ref="AE8:AN8"/>
+    <mergeCell ref="AO8:BI8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="K9:T9"/>
+    <mergeCell ref="U9:AD9"/>
+    <mergeCell ref="AE9:AN9"/>
+    <mergeCell ref="AO9:BI9"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
@@ -2854,29 +2848,14 @@
     <mergeCell ref="R2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="K9:T9"/>
-    <mergeCell ref="U9:AD9"/>
-    <mergeCell ref="AE9:AN9"/>
-    <mergeCell ref="AO9:BI9"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
-    <mergeCell ref="U8:AD8"/>
-    <mergeCell ref="AE8:AN8"/>
-    <mergeCell ref="AO8:BI8"/>
-    <mergeCell ref="A14:BI19"/>
-    <mergeCell ref="A13:BI13"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:T10"/>
-    <mergeCell ref="U10:AD10"/>
-    <mergeCell ref="AE10:AN10"/>
-    <mergeCell ref="AO10:BI10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="K11:T11"/>
-    <mergeCell ref="U11:AD11"/>
-    <mergeCell ref="AE11:AN11"/>
-    <mergeCell ref="AO11:BI11"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -2895,86 +2874,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="42" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="41" t="s">
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="42" t="s">
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="41" t="str">
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="50" t="str">
         <f>クラス仕様!AE1</f>
         <v>商品検索</v>
       </c>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
-      <c r="AQ1" s="42" t="s">
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="42"/>
-      <c r="AS1" s="42"/>
-      <c r="AT1" s="41" t="s">
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="AU1" s="41"/>
-      <c r="AV1" s="41"/>
-      <c r="AW1" s="41"/>
-      <c r="AX1" s="41"/>
-      <c r="AY1" s="41"/>
-      <c r="AZ1" s="41"/>
-      <c r="BA1" s="42" t="s">
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="50"/>
+      <c r="AX1" s="50"/>
+      <c r="AY1" s="50"/>
+      <c r="AZ1" s="50"/>
+      <c r="BA1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="BB1" s="42"/>
-      <c r="BC1" s="42"/>
-      <c r="BD1" s="39">
+      <c r="BB1" s="49"/>
+      <c r="BC1" s="49"/>
+      <c r="BD1" s="51">
         <v>45000</v>
       </c>
-      <c r="BE1" s="39"/>
-      <c r="BF1" s="39"/>
-      <c r="BG1" s="39"/>
-      <c r="BH1" s="39"/>
-      <c r="BI1" s="39"/>
+      <c r="BE1" s="51"/>
+      <c r="BF1" s="51"/>
+      <c r="BG1" s="51"/>
+      <c r="BH1" s="51"/>
+      <c r="BI1" s="51"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3174,82 +3153,82 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="42" t="s">
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="42" t="s">
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="41" t="str">
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="50" t="str">
         <f>クラス仕様!G5</f>
         <v>ItemSerchService</v>
       </c>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="41"/>
-      <c r="AM2" s="41"/>
-      <c r="AN2" s="41"/>
-      <c r="AO2" s="41"/>
-      <c r="AP2" s="41"/>
-      <c r="AQ2" s="42" t="s">
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="50"/>
+      <c r="AQ2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AR2" s="42"/>
-      <c r="AS2" s="42"/>
-      <c r="AT2" s="41" t="s">
+      <c r="AR2" s="49"/>
+      <c r="AS2" s="49"/>
+      <c r="AT2" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="AU2" s="41"/>
-      <c r="AV2" s="41"/>
-      <c r="AW2" s="41"/>
-      <c r="AX2" s="41"/>
-      <c r="AY2" s="41"/>
-      <c r="AZ2" s="41"/>
-      <c r="BA2" s="42" t="s">
+      <c r="AU2" s="50"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="50"/>
+      <c r="AZ2" s="50"/>
+      <c r="BA2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="BB2" s="42"/>
-      <c r="BC2" s="42"/>
-      <c r="BD2" s="53">
+      <c r="BB2" s="49"/>
+      <c r="BC2" s="49"/>
+      <c r="BD2" s="57">
         <v>45568</v>
       </c>
-      <c r="BE2" s="54"/>
-      <c r="BF2" s="54"/>
-      <c r="BG2" s="54"/>
-      <c r="BH2" s="54"/>
-      <c r="BI2" s="55"/>
+      <c r="BE2" s="58"/>
+      <c r="BF2" s="58"/>
+      <c r="BG2" s="58"/>
+      <c r="BH2" s="58"/>
+      <c r="BI2" s="59"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3512,71 +3491,71 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38" t="s">
-        <v>79</v>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53" t="s">
+        <v>75</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="53"/>
+      <c r="U4" s="53"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="53"/>
+      <c r="X4" s="53"/>
+      <c r="Y4" s="53"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="53"/>
+      <c r="AB4" s="53"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="53"/>
+      <c r="AE4" s="53"/>
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="53"/>
+      <c r="AH4" s="53"/>
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="53"/>
+      <c r="AK4" s="53"/>
+      <c r="AL4" s="53"/>
+      <c r="AM4" s="53"/>
+      <c r="AN4" s="53"/>
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="53"/>
+      <c r="AQ4" s="53"/>
+      <c r="AR4" s="53"/>
+      <c r="AS4" s="53"/>
+      <c r="AT4" s="53"/>
+      <c r="AU4" s="53"/>
+      <c r="AV4" s="53"/>
+      <c r="AW4" s="53"/>
+      <c r="AX4" s="53"/>
+      <c r="AY4" s="53"/>
+      <c r="AZ4" s="53"/>
+      <c r="BA4" s="53"/>
+      <c r="BB4" s="53"/>
+      <c r="BC4" s="53"/>
+      <c r="BD4" s="53"/>
+      <c r="BE4" s="53"/>
+      <c r="BF4" s="53"/>
+      <c r="BG4" s="53"/>
+      <c r="BH4" s="53"/>
+      <c r="BI4" s="53"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -3776,71 +3755,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38" t="s">
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="53"/>
+      <c r="U5" s="53"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="53"/>
+      <c r="AB5" s="53"/>
+      <c r="AC5" s="53"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="53"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
+      <c r="AL5" s="53"/>
+      <c r="AM5" s="53"/>
+      <c r="AN5" s="53"/>
+      <c r="AO5" s="53"/>
+      <c r="AP5" s="53"/>
+      <c r="AQ5" s="53"/>
+      <c r="AR5" s="53"/>
+      <c r="AS5" s="53"/>
+      <c r="AT5" s="53"/>
+      <c r="AU5" s="53"/>
+      <c r="AV5" s="53"/>
+      <c r="AW5" s="53"/>
+      <c r="AX5" s="53"/>
+      <c r="AY5" s="53"/>
+      <c r="AZ5" s="53"/>
+      <c r="BA5" s="53"/>
+      <c r="BB5" s="53"/>
+      <c r="BC5" s="53"/>
+      <c r="BD5" s="53"/>
+      <c r="BE5" s="53"/>
+      <c r="BF5" s="53"/>
+      <c r="BG5" s="53"/>
+      <c r="BH5" s="53"/>
+      <c r="BI5" s="53"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -4300,75 +4279,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46" t="s">
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46" t="s">
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="46"/>
-      <c r="AB7" s="46"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="46"/>
-      <c r="AE7" s="46" t="s">
+      <c r="Q7" s="63"/>
+      <c r="R7" s="63"/>
+      <c r="S7" s="63"/>
+      <c r="T7" s="63"/>
+      <c r="U7" s="63"/>
+      <c r="V7" s="63"/>
+      <c r="W7" s="63"/>
+      <c r="X7" s="63"/>
+      <c r="Y7" s="63"/>
+      <c r="Z7" s="63"/>
+      <c r="AA7" s="63"/>
+      <c r="AB7" s="63"/>
+      <c r="AC7" s="63"/>
+      <c r="AD7" s="63"/>
+      <c r="AE7" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="AF7" s="46"/>
-      <c r="AG7" s="46"/>
-      <c r="AH7" s="46"/>
-      <c r="AI7" s="46"/>
-      <c r="AJ7" s="46"/>
-      <c r="AK7" s="46"/>
-      <c r="AL7" s="46"/>
-      <c r="AM7" s="46"/>
-      <c r="AN7" s="46"/>
-      <c r="AO7" s="46"/>
-      <c r="AP7" s="46"/>
-      <c r="AQ7" s="46"/>
-      <c r="AR7" s="46"/>
-      <c r="AS7" s="46"/>
-      <c r="AT7" s="46"/>
-      <c r="AU7" s="46"/>
-      <c r="AV7" s="46"/>
-      <c r="AW7" s="46"/>
-      <c r="AX7" s="46"/>
-      <c r="AY7" s="46"/>
-      <c r="AZ7" s="46"/>
-      <c r="BA7" s="46"/>
-      <c r="BB7" s="46"/>
-      <c r="BC7" s="46"/>
-      <c r="BD7" s="46"/>
-      <c r="BE7" s="46"/>
-      <c r="BF7" s="46"/>
-      <c r="BG7" s="46"/>
-      <c r="BH7" s="46"/>
-      <c r="BI7" s="46"/>
+      <c r="AF7" s="63"/>
+      <c r="AG7" s="63"/>
+      <c r="AH7" s="63"/>
+      <c r="AI7" s="63"/>
+      <c r="AJ7" s="63"/>
+      <c r="AK7" s="63"/>
+      <c r="AL7" s="63"/>
+      <c r="AM7" s="63"/>
+      <c r="AN7" s="63"/>
+      <c r="AO7" s="63"/>
+      <c r="AP7" s="63"/>
+      <c r="AQ7" s="63"/>
+      <c r="AR7" s="63"/>
+      <c r="AS7" s="63"/>
+      <c r="AT7" s="63"/>
+      <c r="AU7" s="63"/>
+      <c r="AV7" s="63"/>
+      <c r="AW7" s="63"/>
+      <c r="AX7" s="63"/>
+      <c r="AY7" s="63"/>
+      <c r="AZ7" s="63"/>
+      <c r="BA7" s="63"/>
+      <c r="BB7" s="63"/>
+      <c r="BC7" s="63"/>
+      <c r="BD7" s="63"/>
+      <c r="BE7" s="63"/>
+      <c r="BF7" s="63"/>
+      <c r="BG7" s="63"/>
+      <c r="BH7" s="63"/>
+      <c r="BI7" s="63"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -4568,75 +4547,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="50" t="s">
+      <c r="B8" s="65"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="50" t="s">
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="52"/>
-      <c r="AE8" s="50" t="s">
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="66"/>
+      <c r="AE8" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
-      <c r="AH8" s="51"/>
-      <c r="AI8" s="51"/>
-      <c r="AJ8" s="51"/>
-      <c r="AK8" s="51"/>
-      <c r="AL8" s="51"/>
-      <c r="AM8" s="51"/>
-      <c r="AN8" s="51"/>
-      <c r="AO8" s="51"/>
-      <c r="AP8" s="51"/>
-      <c r="AQ8" s="51"/>
-      <c r="AR8" s="51"/>
-      <c r="AS8" s="51"/>
-      <c r="AT8" s="51"/>
-      <c r="AU8" s="51"/>
-      <c r="AV8" s="51"/>
-      <c r="AW8" s="51"/>
-      <c r="AX8" s="51"/>
-      <c r="AY8" s="51"/>
-      <c r="AZ8" s="51"/>
-      <c r="BA8" s="51"/>
-      <c r="BB8" s="51"/>
-      <c r="BC8" s="51"/>
-      <c r="BD8" s="51"/>
-      <c r="BE8" s="51"/>
-      <c r="BF8" s="51"/>
-      <c r="BG8" s="51"/>
-      <c r="BH8" s="51"/>
-      <c r="BI8" s="52"/>
+      <c r="AF8" s="65"/>
+      <c r="AG8" s="65"/>
+      <c r="AH8" s="65"/>
+      <c r="AI8" s="65"/>
+      <c r="AJ8" s="65"/>
+      <c r="AK8" s="65"/>
+      <c r="AL8" s="65"/>
+      <c r="AM8" s="65"/>
+      <c r="AN8" s="65"/>
+      <c r="AO8" s="65"/>
+      <c r="AP8" s="65"/>
+      <c r="AQ8" s="65"/>
+      <c r="AR8" s="65"/>
+      <c r="AS8" s="65"/>
+      <c r="AT8" s="65"/>
+      <c r="AU8" s="65"/>
+      <c r="AV8" s="65"/>
+      <c r="AW8" s="65"/>
+      <c r="AX8" s="65"/>
+      <c r="AY8" s="65"/>
+      <c r="AZ8" s="65"/>
+      <c r="BA8" s="65"/>
+      <c r="BB8" s="65"/>
+      <c r="BC8" s="65"/>
+      <c r="BD8" s="65"/>
+      <c r="BE8" s="65"/>
+      <c r="BF8" s="65"/>
+      <c r="BG8" s="65"/>
+      <c r="BH8" s="65"/>
+      <c r="BI8" s="66"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -4836,75 +4815,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="47" t="s">
+      <c r="B9" s="61"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="49"/>
-      <c r="P9" s="47" t="s">
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="61"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="47" t="s">
+      <c r="Q9" s="61"/>
+      <c r="R9" s="61"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="61"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="61"/>
+      <c r="W9" s="61"/>
+      <c r="X9" s="61"/>
+      <c r="Y9" s="61"/>
+      <c r="Z9" s="61"/>
+      <c r="AA9" s="61"/>
+      <c r="AB9" s="61"/>
+      <c r="AC9" s="61"/>
+      <c r="AD9" s="62"/>
+      <c r="AE9" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="48"/>
-      <c r="AH9" s="48"/>
-      <c r="AI9" s="48"/>
-      <c r="AJ9" s="48"/>
-      <c r="AK9" s="48"/>
-      <c r="AL9" s="48"/>
-      <c r="AM9" s="48"/>
-      <c r="AN9" s="48"/>
-      <c r="AO9" s="48"/>
-      <c r="AP9" s="48"/>
-      <c r="AQ9" s="48"/>
-      <c r="AR9" s="48"/>
-      <c r="AS9" s="48"/>
-      <c r="AT9" s="48"/>
-      <c r="AU9" s="48"/>
-      <c r="AV9" s="48"/>
-      <c r="AW9" s="48"/>
-      <c r="AX9" s="48"/>
-      <c r="AY9" s="48"/>
-      <c r="AZ9" s="48"/>
-      <c r="BA9" s="48"/>
-      <c r="BB9" s="48"/>
-      <c r="BC9" s="48"/>
-      <c r="BD9" s="48"/>
-      <c r="BE9" s="48"/>
-      <c r="BF9" s="48"/>
-      <c r="BG9" s="48"/>
-      <c r="BH9" s="48"/>
-      <c r="BI9" s="49"/>
+      <c r="AF9" s="61"/>
+      <c r="AG9" s="61"/>
+      <c r="AH9" s="61"/>
+      <c r="AI9" s="61"/>
+      <c r="AJ9" s="61"/>
+      <c r="AK9" s="61"/>
+      <c r="AL9" s="61"/>
+      <c r="AM9" s="61"/>
+      <c r="AN9" s="61"/>
+      <c r="AO9" s="61"/>
+      <c r="AP9" s="61"/>
+      <c r="AQ9" s="61"/>
+      <c r="AR9" s="61"/>
+      <c r="AS9" s="61"/>
+      <c r="AT9" s="61"/>
+      <c r="AU9" s="61"/>
+      <c r="AV9" s="61"/>
+      <c r="AW9" s="61"/>
+      <c r="AX9" s="61"/>
+      <c r="AY9" s="61"/>
+      <c r="AZ9" s="61"/>
+      <c r="BA9" s="61"/>
+      <c r="BB9" s="61"/>
+      <c r="BC9" s="61"/>
+      <c r="BD9" s="61"/>
+      <c r="BE9" s="61"/>
+      <c r="BF9" s="61"/>
+      <c r="BG9" s="61"/>
+      <c r="BH9" s="61"/>
+      <c r="BI9" s="62"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -5104,73 +5083,73 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="45" t="s">
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45" t="s">
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="45"/>
-      <c r="Z10" s="45"/>
-      <c r="AA10" s="45"/>
-      <c r="AB10" s="45"/>
-      <c r="AC10" s="45"/>
-      <c r="AD10" s="45"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="45"/>
-      <c r="AJ10" s="45"/>
-      <c r="AK10" s="45"/>
-      <c r="AL10" s="45"/>
-      <c r="AM10" s="45"/>
-      <c r="AN10" s="45"/>
-      <c r="AO10" s="45"/>
-      <c r="AP10" s="45"/>
-      <c r="AQ10" s="45"/>
-      <c r="AR10" s="45"/>
-      <c r="AS10" s="45"/>
-      <c r="AT10" s="45"/>
-      <c r="AU10" s="45"/>
-      <c r="AV10" s="45"/>
-      <c r="AW10" s="45"/>
-      <c r="AX10" s="45"/>
-      <c r="AY10" s="45"/>
-      <c r="AZ10" s="45"/>
-      <c r="BA10" s="45"/>
-      <c r="BB10" s="45"/>
-      <c r="BC10" s="45"/>
-      <c r="BD10" s="45"/>
-      <c r="BE10" s="45"/>
-      <c r="BF10" s="45"/>
-      <c r="BG10" s="45"/>
-      <c r="BH10" s="45"/>
-      <c r="BI10" s="45"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="68"/>
+      <c r="T10" s="68"/>
+      <c r="U10" s="68"/>
+      <c r="V10" s="68"/>
+      <c r="W10" s="68"/>
+      <c r="X10" s="68"/>
+      <c r="Y10" s="68"/>
+      <c r="Z10" s="68"/>
+      <c r="AA10" s="68"/>
+      <c r="AB10" s="68"/>
+      <c r="AC10" s="68"/>
+      <c r="AD10" s="68"/>
+      <c r="AE10" s="68"/>
+      <c r="AF10" s="68"/>
+      <c r="AG10" s="68"/>
+      <c r="AH10" s="68"/>
+      <c r="AI10" s="68"/>
+      <c r="AJ10" s="68"/>
+      <c r="AK10" s="68"/>
+      <c r="AL10" s="68"/>
+      <c r="AM10" s="68"/>
+      <c r="AN10" s="68"/>
+      <c r="AO10" s="68"/>
+      <c r="AP10" s="68"/>
+      <c r="AQ10" s="68"/>
+      <c r="AR10" s="68"/>
+      <c r="AS10" s="68"/>
+      <c r="AT10" s="68"/>
+      <c r="AU10" s="68"/>
+      <c r="AV10" s="68"/>
+      <c r="AW10" s="68"/>
+      <c r="AX10" s="68"/>
+      <c r="AY10" s="68"/>
+      <c r="AZ10" s="68"/>
+      <c r="BA10" s="68"/>
+      <c r="BB10" s="68"/>
+      <c r="BC10" s="68"/>
+      <c r="BD10" s="68"/>
+      <c r="BE10" s="68"/>
+      <c r="BF10" s="68"/>
+      <c r="BG10" s="68"/>
+      <c r="BH10" s="68"/>
+      <c r="BI10" s="68"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -5370,73 +5349,73 @@
       <c r="IX10" s="1"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36" t="s">
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="36"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="36"/>
-      <c r="AD11" s="36"/>
-      <c r="AE11" s="36" t="s">
+      <c r="Q11" s="56"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="56"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="56"/>
+      <c r="Z11" s="56"/>
+      <c r="AA11" s="56"/>
+      <c r="AB11" s="56"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="56"/>
+      <c r="AE11" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="AF11" s="36"/>
-      <c r="AG11" s="36"/>
-      <c r="AH11" s="36"/>
-      <c r="AI11" s="36"/>
-      <c r="AJ11" s="36"/>
-      <c r="AK11" s="36"/>
-      <c r="AL11" s="36"/>
-      <c r="AM11" s="36"/>
-      <c r="AN11" s="36"/>
-      <c r="AO11" s="36"/>
-      <c r="AP11" s="36"/>
-      <c r="AQ11" s="36"/>
-      <c r="AR11" s="36"/>
-      <c r="AS11" s="36"/>
-      <c r="AT11" s="36"/>
-      <c r="AU11" s="36"/>
-      <c r="AV11" s="36"/>
-      <c r="AW11" s="36"/>
-      <c r="AX11" s="36"/>
-      <c r="AY11" s="36"/>
-      <c r="AZ11" s="36"/>
-      <c r="BA11" s="36"/>
-      <c r="BB11" s="36"/>
-      <c r="BC11" s="36"/>
-      <c r="BD11" s="36"/>
-      <c r="BE11" s="36"/>
-      <c r="BF11" s="36"/>
-      <c r="BG11" s="36"/>
-      <c r="BH11" s="36"/>
-      <c r="BI11" s="36"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="56"/>
+      <c r="AH11" s="56"/>
+      <c r="AI11" s="56"/>
+      <c r="AJ11" s="56"/>
+      <c r="AK11" s="56"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="56"/>
+      <c r="AN11" s="56"/>
+      <c r="AO11" s="56"/>
+      <c r="AP11" s="56"/>
+      <c r="AQ11" s="56"/>
+      <c r="AR11" s="56"/>
+      <c r="AS11" s="56"/>
+      <c r="AT11" s="56"/>
+      <c r="AU11" s="56"/>
+      <c r="AV11" s="56"/>
+      <c r="AW11" s="56"/>
+      <c r="AX11" s="56"/>
+      <c r="AY11" s="56"/>
+      <c r="AZ11" s="56"/>
+      <c r="BA11" s="56"/>
+      <c r="BB11" s="56"/>
+      <c r="BC11" s="56"/>
+      <c r="BD11" s="56"/>
+      <c r="BE11" s="56"/>
+      <c r="BF11" s="56"/>
+      <c r="BG11" s="56"/>
+      <c r="BH11" s="56"/>
+      <c r="BI11" s="56"/>
       <c r="BJ11" s="1"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
@@ -5636,73 +5615,73 @@
       <c r="IX11" s="1"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45" t="s">
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="45"/>
-      <c r="W12" s="45"/>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="45"/>
-      <c r="Z12" s="45"/>
-      <c r="AA12" s="45"/>
-      <c r="AB12" s="45"/>
-      <c r="AC12" s="45"/>
-      <c r="AD12" s="45"/>
-      <c r="AE12" s="45" t="s">
+      <c r="Q12" s="68"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="68"/>
+      <c r="T12" s="68"/>
+      <c r="U12" s="68"/>
+      <c r="V12" s="68"/>
+      <c r="W12" s="68"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="68"/>
+      <c r="Z12" s="68"/>
+      <c r="AA12" s="68"/>
+      <c r="AB12" s="68"/>
+      <c r="AC12" s="68"/>
+      <c r="AD12" s="68"/>
+      <c r="AE12" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="AF12" s="45"/>
-      <c r="AG12" s="45"/>
-      <c r="AH12" s="45"/>
-      <c r="AI12" s="45"/>
-      <c r="AJ12" s="45"/>
-      <c r="AK12" s="45"/>
-      <c r="AL12" s="45"/>
-      <c r="AM12" s="45"/>
-      <c r="AN12" s="45"/>
-      <c r="AO12" s="45"/>
-      <c r="AP12" s="45"/>
-      <c r="AQ12" s="45"/>
-      <c r="AR12" s="45"/>
-      <c r="AS12" s="45"/>
-      <c r="AT12" s="45"/>
-      <c r="AU12" s="45"/>
-      <c r="AV12" s="45"/>
-      <c r="AW12" s="45"/>
-      <c r="AX12" s="45"/>
-      <c r="AY12" s="45"/>
-      <c r="AZ12" s="45"/>
-      <c r="BA12" s="45"/>
-      <c r="BB12" s="45"/>
-      <c r="BC12" s="45"/>
-      <c r="BD12" s="45"/>
-      <c r="BE12" s="45"/>
-      <c r="BF12" s="45"/>
-      <c r="BG12" s="45"/>
-      <c r="BH12" s="45"/>
-      <c r="BI12" s="45"/>
+      <c r="AF12" s="68"/>
+      <c r="AG12" s="68"/>
+      <c r="AH12" s="68"/>
+      <c r="AI12" s="68"/>
+      <c r="AJ12" s="68"/>
+      <c r="AK12" s="68"/>
+      <c r="AL12" s="68"/>
+      <c r="AM12" s="68"/>
+      <c r="AN12" s="68"/>
+      <c r="AO12" s="68"/>
+      <c r="AP12" s="68"/>
+      <c r="AQ12" s="68"/>
+      <c r="AR12" s="68"/>
+      <c r="AS12" s="68"/>
+      <c r="AT12" s="68"/>
+      <c r="AU12" s="68"/>
+      <c r="AV12" s="68"/>
+      <c r="AW12" s="68"/>
+      <c r="AX12" s="68"/>
+      <c r="AY12" s="68"/>
+      <c r="AZ12" s="68"/>
+      <c r="BA12" s="68"/>
+      <c r="BB12" s="68"/>
+      <c r="BC12" s="68"/>
+      <c r="BD12" s="68"/>
+      <c r="BE12" s="68"/>
+      <c r="BF12" s="68"/>
+      <c r="BG12" s="68"/>
+      <c r="BH12" s="68"/>
+      <c r="BI12" s="68"/>
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
@@ -6162,73 +6141,73 @@
       <c r="IX13" s="1"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="46" t="s">
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="46"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="46"/>
-      <c r="Y14" s="46"/>
-      <c r="Z14" s="46"/>
-      <c r="AA14" s="46"/>
-      <c r="AB14" s="46"/>
-      <c r="AC14" s="46"/>
-      <c r="AD14" s="46"/>
-      <c r="AE14" s="46"/>
-      <c r="AF14" s="46"/>
-      <c r="AG14" s="46"/>
-      <c r="AH14" s="46"/>
-      <c r="AI14" s="46"/>
-      <c r="AJ14" s="46"/>
-      <c r="AK14" s="46"/>
-      <c r="AL14" s="46"/>
-      <c r="AM14" s="46"/>
-      <c r="AN14" s="46"/>
-      <c r="AO14" s="46"/>
-      <c r="AP14" s="46"/>
-      <c r="AQ14" s="46"/>
-      <c r="AR14" s="46"/>
-      <c r="AS14" s="46"/>
-      <c r="AT14" s="46" t="s">
+      <c r="Q14" s="63"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
+      <c r="T14" s="63"/>
+      <c r="U14" s="63"/>
+      <c r="V14" s="63"/>
+      <c r="W14" s="63"/>
+      <c r="X14" s="63"/>
+      <c r="Y14" s="63"/>
+      <c r="Z14" s="63"/>
+      <c r="AA14" s="63"/>
+      <c r="AB14" s="63"/>
+      <c r="AC14" s="63"/>
+      <c r="AD14" s="63"/>
+      <c r="AE14" s="63"/>
+      <c r="AF14" s="63"/>
+      <c r="AG14" s="63"/>
+      <c r="AH14" s="63"/>
+      <c r="AI14" s="63"/>
+      <c r="AJ14" s="63"/>
+      <c r="AK14" s="63"/>
+      <c r="AL14" s="63"/>
+      <c r="AM14" s="63"/>
+      <c r="AN14" s="63"/>
+      <c r="AO14" s="63"/>
+      <c r="AP14" s="63"/>
+      <c r="AQ14" s="63"/>
+      <c r="AR14" s="63"/>
+      <c r="AS14" s="63"/>
+      <c r="AT14" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="AU14" s="46"/>
-      <c r="AV14" s="46"/>
-      <c r="AW14" s="46"/>
-      <c r="AX14" s="46"/>
-      <c r="AY14" s="46"/>
-      <c r="AZ14" s="46"/>
-      <c r="BA14" s="46"/>
-      <c r="BB14" s="46"/>
-      <c r="BC14" s="46"/>
-      <c r="BD14" s="46"/>
-      <c r="BE14" s="46"/>
-      <c r="BF14" s="46"/>
-      <c r="BG14" s="46"/>
-      <c r="BH14" s="46"/>
-      <c r="BI14" s="46"/>
+      <c r="AU14" s="63"/>
+      <c r="AV14" s="63"/>
+      <c r="AW14" s="63"/>
+      <c r="AX14" s="63"/>
+      <c r="AY14" s="63"/>
+      <c r="AZ14" s="63"/>
+      <c r="BA14" s="63"/>
+      <c r="BB14" s="63"/>
+      <c r="BC14" s="63"/>
+      <c r="BD14" s="63"/>
+      <c r="BE14" s="63"/>
+      <c r="BF14" s="63"/>
+      <c r="BG14" s="63"/>
+      <c r="BH14" s="63"/>
+      <c r="BI14" s="63"/>
       <c r="BJ14" s="1"/>
       <c r="BK14" s="1"/>
       <c r="BL14" s="1"/>
@@ -6479,7 +6458,7 @@
       <c r="AS15" s="9"/>
       <c r="AT15" s="5"/>
       <c r="AU15" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AV15" s="6"/>
       <c r="AW15" s="6"/>
@@ -6974,7 +6953,7 @@
       <c r="O17" s="13"/>
       <c r="P17" s="34"/>
       <c r="Q17" s="32" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="T17" s="15"/>
       <c r="U17" s="15"/>
@@ -7488,11 +7467,11 @@
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="13"/>
-      <c r="P19" s="56" t="s">
+      <c r="P19" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="37"/>
       <c r="T19" s="15"/>
       <c r="U19" s="15"/>
       <c r="V19" s="15"/>
@@ -7748,11 +7727,11 @@
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
       <c r="O20" s="13"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="57" t="s">
+      <c r="P20" s="36"/>
+      <c r="Q20" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="R20" s="57"/>
+      <c r="R20" s="37"/>
       <c r="T20" s="15"/>
       <c r="U20" s="15"/>
       <c r="V20" s="15"/>
@@ -8008,9 +7987,9 @@
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
       <c r="O21" s="13"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="57"/>
-      <c r="R21" s="57" t="s">
+      <c r="P21" s="36"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="37" t="s">
         <v>57</v>
       </c>
       <c r="T21" s="15"/>
@@ -8268,8 +8247,8 @@
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
       <c r="O22" s="13"/>
-      <c r="P22" s="56"/>
-      <c r="R22" s="57" t="s">
+      <c r="P22" s="36"/>
+      <c r="R22" s="37" t="s">
         <v>58</v>
       </c>
       <c r="S22" s="27"/>
@@ -8528,7 +8507,7 @@
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
       <c r="O23" s="13"/>
-      <c r="P23" s="56"/>
+      <c r="P23" s="36"/>
       <c r="S23" s="15"/>
       <c r="T23" s="15"/>
       <c r="U23" s="15"/>
@@ -8787,7 +8766,7 @@
       <c r="N24" s="12"/>
       <c r="O24" s="13"/>
       <c r="P24" s="14" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="Q24" s="15"/>
       <c r="R24" s="15"/>
@@ -9049,10 +9028,10 @@
       <c r="N25" s="12"/>
       <c r="O25" s="13"/>
       <c r="P25" s="30"/>
-      <c r="Q25" s="57" t="s">
-        <v>64</v>
+      <c r="Q25" s="37" t="s">
+        <v>62</v>
       </c>
-      <c r="S25" s="57"/>
+      <c r="S25" s="37"/>
       <c r="U25" s="18"/>
       <c r="V25" s="18"/>
       <c r="W25" s="15"/>
@@ -9309,10 +9288,10 @@
       <c r="N26" s="12"/>
       <c r="O26" s="13"/>
       <c r="P26" s="30"/>
-      <c r="R26" s="58" t="s">
-        <v>69</v>
+      <c r="R26" s="38" t="s">
+        <v>66</v>
       </c>
-      <c r="S26" s="57"/>
+      <c r="S26" s="37"/>
       <c r="U26" s="29"/>
       <c r="V26" s="18"/>
       <c r="W26" s="15"/>
@@ -9569,9 +9548,9 @@
       <c r="N27" s="12"/>
       <c r="O27" s="13"/>
       <c r="P27" s="30"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="58" t="s">
-        <v>60</v>
+      <c r="R27" s="38"/>
+      <c r="S27" s="38" t="s">
+        <v>59</v>
       </c>
       <c r="T27" s="15"/>
       <c r="W27" s="15"/>
@@ -9828,8 +9807,8 @@
       <c r="N28" s="12"/>
       <c r="O28" s="13"/>
       <c r="P28" s="30"/>
-      <c r="R28" s="58"/>
-      <c r="S28" s="57"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="37"/>
       <c r="U28" s="18"/>
       <c r="V28" s="18"/>
       <c r="W28" s="15"/>
@@ -10086,6 +10065,9 @@
       <c r="N29" s="12"/>
       <c r="O29" s="13"/>
       <c r="P29" s="30"/>
+      <c r="R29" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="U29" s="29"/>
       <c r="V29" s="18"/>
       <c r="W29" s="15"/>
@@ -10342,8 +10324,9 @@
       <c r="N30" s="12"/>
       <c r="O30" s="13"/>
       <c r="P30" s="30"/>
-      <c r="R30" s="2" t="s">
-        <v>70</v>
+      <c r="R30" s="38"/>
+      <c r="S30" s="37" t="s">
+        <v>60</v>
       </c>
       <c r="T30" s="15"/>
       <c r="W30" s="15"/>
@@ -10600,9 +10583,9 @@
       <c r="N31" s="12"/>
       <c r="O31" s="13"/>
       <c r="P31" s="30"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="57" t="s">
-        <v>61</v>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38" t="s">
+        <v>63</v>
       </c>
       <c r="T31" s="15"/>
       <c r="W31" s="15"/>
@@ -10859,10 +10842,7 @@
       <c r="N32" s="12"/>
       <c r="O32" s="13"/>
       <c r="P32" s="30"/>
-      <c r="R32" s="58"/>
-      <c r="S32" s="58" t="s">
-        <v>66</v>
-      </c>
+      <c r="R32" s="37"/>
       <c r="T32" s="15"/>
       <c r="U32" s="27"/>
       <c r="W32" s="15"/>
@@ -11119,7 +11099,10 @@
       <c r="N33" s="12"/>
       <c r="O33" s="13"/>
       <c r="P33" s="30"/>
-      <c r="R33" s="57"/>
+      <c r="R33" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="S33" s="38"/>
       <c r="T33" s="15"/>
       <c r="V33" s="27"/>
       <c r="W33" s="15"/>
@@ -11376,10 +11359,10 @@
       <c r="N34" s="12"/>
       <c r="O34" s="13"/>
       <c r="P34" s="31"/>
-      <c r="R34" s="57" t="s">
-        <v>71</v>
+      <c r="R34" s="37"/>
+      <c r="S34" s="38" t="s">
+        <v>61</v>
       </c>
-      <c r="S34" s="58"/>
       <c r="T34" s="15"/>
       <c r="V34" s="27"/>
       <c r="W34" s="15"/>
@@ -11636,9 +11619,9 @@
       <c r="N35" s="12"/>
       <c r="O35" s="13"/>
       <c r="P35" s="14"/>
-      <c r="R35" s="57"/>
-      <c r="S35" s="58" t="s">
-        <v>62</v>
+      <c r="R35" s="37"/>
+      <c r="S35" s="38" t="s">
+        <v>64</v>
       </c>
       <c r="T35" s="15"/>
       <c r="V35" s="27"/>
@@ -11896,10 +11879,7 @@
       <c r="N36" s="12"/>
       <c r="O36" s="13"/>
       <c r="P36" s="14"/>
-      <c r="R36" s="57"/>
-      <c r="S36" s="58" t="s">
-        <v>67</v>
-      </c>
+      <c r="R36" s="37"/>
       <c r="T36" s="15"/>
       <c r="U36" s="15"/>
       <c r="V36" s="15"/>
@@ -12156,8 +12136,10 @@
       <c r="M37" s="12"/>
       <c r="N37" s="12"/>
       <c r="O37" s="13"/>
-      <c r="P37" s="14"/>
-      <c r="R37" s="57"/>
+      <c r="P37" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="S37" s="38"/>
       <c r="T37" s="15"/>
       <c r="U37" s="15"/>
       <c r="V37" s="15"/>
@@ -12414,10 +12396,11 @@
       <c r="N38" s="12"/>
       <c r="O38" s="13"/>
       <c r="P38" s="14"/>
-      <c r="R38" s="2" t="s">
-        <v>65</v>
+      <c r="Q38" s="2" t="s">
+        <v>70</v>
       </c>
-      <c r="S38" s="58"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
       <c r="T38" s="15"/>
       <c r="U38" s="15"/>
       <c r="V38" s="15"/>
@@ -12674,10 +12657,8 @@
       <c r="N39" s="12"/>
       <c r="O39" s="13"/>
       <c r="P39" s="14"/>
-      <c r="R39" s="58"/>
-      <c r="S39" s="58" t="s">
-        <v>63</v>
-      </c>
+      <c r="R39" s="38"/>
+      <c r="S39" s="38"/>
       <c r="T39" s="15"/>
       <c r="U39" s="15"/>
       <c r="V39" s="15"/>
@@ -12934,10 +12915,7 @@
       <c r="N40" s="12"/>
       <c r="O40" s="13"/>
       <c r="P40" s="14"/>
-      <c r="R40" s="58"/>
-      <c r="S40" s="58" t="s">
-        <v>72</v>
-      </c>
+      <c r="S40" s="38"/>
       <c r="T40" s="15"/>
       <c r="U40" s="15"/>
       <c r="V40" s="15"/>
@@ -13189,9 +13167,6 @@
       <c r="N41" s="12"/>
       <c r="O41" s="13"/>
       <c r="P41" s="14"/>
-      <c r="S41" s="58" t="s">
-        <v>67</v>
-      </c>
       <c r="T41" s="15"/>
       <c r="U41" s="15"/>
       <c r="V41" s="15"/>
@@ -13705,9 +13680,6 @@
       <c r="M43" s="12"/>
       <c r="N43" s="12"/>
       <c r="O43" s="13"/>
-      <c r="P43" s="14" t="s">
-        <v>68</v>
-      </c>
       <c r="T43" s="15"/>
       <c r="U43" s="15"/>
       <c r="V43" s="15"/>
@@ -13964,10 +13936,6 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="13"/>
-      <c r="P44" s="14"/>
-      <c r="Q44" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="T44" s="15"/>
       <c r="U44" s="15"/>
       <c r="V44" s="15"/>
@@ -14208,262 +14176,262 @@
       <c r="IW44" s="1"/>
       <c r="IX44" s="1"/>
     </row>
-    <row r="45" spans="1:258" s="63" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="59"/>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="60"/>
-      <c r="F45" s="60"/>
-      <c r="G45" s="60"/>
-      <c r="H45" s="60"/>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="60"/>
-      <c r="L45" s="60"/>
-      <c r="M45" s="60"/>
-      <c r="N45" s="60"/>
-      <c r="O45" s="61"/>
-      <c r="P45" s="62"/>
-      <c r="T45" s="64"/>
-      <c r="U45" s="64"/>
-      <c r="V45" s="64"/>
-      <c r="W45" s="64"/>
-      <c r="X45" s="64"/>
-      <c r="Y45" s="64"/>
-      <c r="Z45" s="64"/>
-      <c r="AA45" s="64"/>
-      <c r="AB45" s="64"/>
-      <c r="AC45" s="64"/>
-      <c r="AD45" s="64"/>
-      <c r="AE45" s="64"/>
-      <c r="AF45" s="64"/>
-      <c r="AG45" s="64"/>
-      <c r="AH45" s="64"/>
-      <c r="AI45" s="64"/>
-      <c r="AJ45" s="64"/>
-      <c r="AK45" s="64"/>
-      <c r="AL45" s="64"/>
-      <c r="AM45" s="64"/>
-      <c r="AN45" s="64"/>
-      <c r="AO45" s="64"/>
-      <c r="AP45" s="64"/>
-      <c r="AQ45" s="64"/>
-      <c r="AR45" s="64"/>
-      <c r="AS45" s="65"/>
-      <c r="AT45" s="59"/>
-      <c r="AU45" s="60"/>
-      <c r="AV45" s="60"/>
-      <c r="AW45" s="60"/>
-      <c r="AX45" s="60"/>
-      <c r="AY45" s="60"/>
-      <c r="AZ45" s="60"/>
-      <c r="BA45" s="60"/>
-      <c r="BB45" s="60"/>
-      <c r="BC45" s="60"/>
-      <c r="BD45" s="60"/>
-      <c r="BE45" s="60"/>
-      <c r="BF45" s="60"/>
-      <c r="BG45" s="60"/>
-      <c r="BH45" s="60"/>
-      <c r="BI45" s="61"/>
-      <c r="BJ45" s="66"/>
-      <c r="BK45" s="66"/>
-      <c r="BL45" s="66"/>
-      <c r="BM45" s="66"/>
-      <c r="BN45" s="66"/>
-      <c r="BO45" s="66"/>
-      <c r="BP45" s="66"/>
-      <c r="BQ45" s="66"/>
-      <c r="BR45" s="66"/>
-      <c r="BS45" s="66"/>
-      <c r="BT45" s="66"/>
-      <c r="BU45" s="66"/>
-      <c r="BV45" s="66"/>
-      <c r="BW45" s="66"/>
-      <c r="BX45" s="66"/>
-      <c r="BY45" s="66"/>
-      <c r="BZ45" s="66"/>
-      <c r="CA45" s="66"/>
-      <c r="CB45" s="66"/>
-      <c r="CC45" s="66"/>
-      <c r="CD45" s="66"/>
-      <c r="CE45" s="66"/>
-      <c r="CF45" s="66"/>
-      <c r="CG45" s="66"/>
-      <c r="CH45" s="66"/>
-      <c r="CI45" s="66"/>
-      <c r="CJ45" s="66"/>
-      <c r="CK45" s="66"/>
-      <c r="CL45" s="66"/>
-      <c r="CM45" s="66"/>
-      <c r="CN45" s="66"/>
-      <c r="CO45" s="66"/>
-      <c r="CP45" s="66"/>
-      <c r="CQ45" s="66"/>
-      <c r="CR45" s="66"/>
-      <c r="CS45" s="66"/>
-      <c r="CT45" s="66"/>
-      <c r="CU45" s="66"/>
-      <c r="CV45" s="66"/>
-      <c r="CW45" s="66"/>
-      <c r="CX45" s="66"/>
-      <c r="CY45" s="66"/>
-      <c r="CZ45" s="66"/>
-      <c r="DA45" s="66"/>
-      <c r="DB45" s="66"/>
-      <c r="DC45" s="66"/>
-      <c r="DD45" s="66"/>
-      <c r="DE45" s="66"/>
-      <c r="DF45" s="66"/>
-      <c r="DG45" s="66"/>
-      <c r="DH45" s="66"/>
-      <c r="DI45" s="66"/>
-      <c r="DJ45" s="66"/>
-      <c r="DK45" s="66"/>
-      <c r="DL45" s="66"/>
-      <c r="DM45" s="66"/>
-      <c r="DN45" s="66"/>
-      <c r="DO45" s="66"/>
-      <c r="DP45" s="66"/>
-      <c r="DQ45" s="66"/>
-      <c r="DR45" s="66"/>
-      <c r="DS45" s="66"/>
-      <c r="DT45" s="66"/>
-      <c r="DU45" s="66"/>
-      <c r="DV45" s="66"/>
-      <c r="DW45" s="66"/>
-      <c r="DX45" s="66"/>
-      <c r="DY45" s="66"/>
-      <c r="DZ45" s="66"/>
-      <c r="EA45" s="66"/>
-      <c r="EB45" s="66"/>
-      <c r="EC45" s="66"/>
-      <c r="ED45" s="66"/>
-      <c r="EE45" s="66"/>
-      <c r="EF45" s="66"/>
-      <c r="EG45" s="66"/>
-      <c r="EH45" s="66"/>
-      <c r="EI45" s="66"/>
-      <c r="EJ45" s="66"/>
-      <c r="EK45" s="66"/>
-      <c r="EL45" s="66"/>
-      <c r="EM45" s="66"/>
-      <c r="EN45" s="66"/>
-      <c r="EO45" s="66"/>
-      <c r="EP45" s="66"/>
-      <c r="EQ45" s="66"/>
-      <c r="ER45" s="66"/>
-      <c r="ES45" s="66"/>
-      <c r="ET45" s="66"/>
-      <c r="EU45" s="66"/>
-      <c r="EV45" s="66"/>
-      <c r="EW45" s="66"/>
-      <c r="EX45" s="66"/>
-      <c r="EY45" s="66"/>
-      <c r="EZ45" s="66"/>
-      <c r="FA45" s="66"/>
-      <c r="FB45" s="66"/>
-      <c r="FC45" s="66"/>
-      <c r="FD45" s="66"/>
-      <c r="FE45" s="66"/>
-      <c r="FF45" s="66"/>
-      <c r="FG45" s="66"/>
-      <c r="FH45" s="66"/>
-      <c r="FI45" s="66"/>
-      <c r="FJ45" s="66"/>
-      <c r="FK45" s="66"/>
-      <c r="FL45" s="66"/>
-      <c r="FM45" s="66"/>
-      <c r="FN45" s="66"/>
-      <c r="FO45" s="66"/>
-      <c r="FP45" s="66"/>
-      <c r="FQ45" s="66"/>
-      <c r="FR45" s="66"/>
-      <c r="FS45" s="66"/>
-      <c r="FT45" s="66"/>
-      <c r="FU45" s="66"/>
-      <c r="FV45" s="66"/>
-      <c r="FW45" s="66"/>
-      <c r="FX45" s="66"/>
-      <c r="FY45" s="66"/>
-      <c r="FZ45" s="66"/>
-      <c r="GA45" s="66"/>
-      <c r="GB45" s="66"/>
-      <c r="GC45" s="66"/>
-      <c r="GD45" s="66"/>
-      <c r="GE45" s="66"/>
-      <c r="GF45" s="66"/>
-      <c r="GG45" s="66"/>
-      <c r="GH45" s="66"/>
-      <c r="GI45" s="66"/>
-      <c r="GJ45" s="66"/>
-      <c r="GK45" s="66"/>
-      <c r="GL45" s="66"/>
-      <c r="GM45" s="66"/>
-      <c r="GN45" s="66"/>
-      <c r="GO45" s="66"/>
-      <c r="GP45" s="66"/>
-      <c r="GQ45" s="66"/>
-      <c r="GR45" s="66"/>
-      <c r="GS45" s="66"/>
-      <c r="GT45" s="66"/>
-      <c r="GU45" s="66"/>
-      <c r="GV45" s="66"/>
-      <c r="GW45" s="66"/>
-      <c r="GX45" s="66"/>
-      <c r="GY45" s="66"/>
-      <c r="GZ45" s="66"/>
-      <c r="HA45" s="66"/>
-      <c r="HB45" s="66"/>
-      <c r="HC45" s="66"/>
-      <c r="HD45" s="66"/>
-      <c r="HE45" s="66"/>
-      <c r="HF45" s="66"/>
-      <c r="HG45" s="66"/>
-      <c r="HH45" s="66"/>
-      <c r="HI45" s="66"/>
-      <c r="HJ45" s="66"/>
-      <c r="HK45" s="66"/>
-      <c r="HL45" s="66"/>
-      <c r="HM45" s="66"/>
-      <c r="HN45" s="66"/>
-      <c r="HO45" s="66"/>
-      <c r="HP45" s="66"/>
-      <c r="HQ45" s="66"/>
-      <c r="HR45" s="66"/>
-      <c r="HS45" s="66"/>
-      <c r="HT45" s="66"/>
-      <c r="HU45" s="66"/>
-      <c r="HV45" s="66"/>
-      <c r="HW45" s="66"/>
-      <c r="HX45" s="66"/>
-      <c r="HY45" s="66"/>
-      <c r="HZ45" s="66"/>
-      <c r="IA45" s="66"/>
-      <c r="IB45" s="66"/>
-      <c r="IC45" s="66"/>
-      <c r="ID45" s="66"/>
-      <c r="IE45" s="66"/>
-      <c r="IF45" s="66"/>
-      <c r="IG45" s="66"/>
-      <c r="IH45" s="66"/>
-      <c r="II45" s="66"/>
-      <c r="IJ45" s="66"/>
-      <c r="IK45" s="66"/>
-      <c r="IL45" s="66"/>
-      <c r="IM45" s="66"/>
-      <c r="IN45" s="66"/>
-      <c r="IO45" s="66"/>
-      <c r="IP45" s="66"/>
-      <c r="IQ45" s="66"/>
-      <c r="IR45" s="66"/>
-      <c r="IS45" s="66"/>
-      <c r="IT45" s="66"/>
-      <c r="IU45" s="66"/>
-      <c r="IV45" s="66"/>
-      <c r="IW45" s="66"/>
-      <c r="IX45" s="66"/>
+    <row r="45" spans="1:258" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="39"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="40"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="41"/>
+      <c r="P45" s="42"/>
+      <c r="T45" s="44"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="44"/>
+      <c r="W45" s="44"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="44"/>
+      <c r="Z45" s="44"/>
+      <c r="AA45" s="44"/>
+      <c r="AB45" s="44"/>
+      <c r="AC45" s="44"/>
+      <c r="AD45" s="44"/>
+      <c r="AE45" s="44"/>
+      <c r="AF45" s="44"/>
+      <c r="AG45" s="44"/>
+      <c r="AH45" s="44"/>
+      <c r="AI45" s="44"/>
+      <c r="AJ45" s="44"/>
+      <c r="AK45" s="44"/>
+      <c r="AL45" s="44"/>
+      <c r="AM45" s="44"/>
+      <c r="AN45" s="44"/>
+      <c r="AO45" s="44"/>
+      <c r="AP45" s="44"/>
+      <c r="AQ45" s="44"/>
+      <c r="AR45" s="44"/>
+      <c r="AS45" s="45"/>
+      <c r="AT45" s="39"/>
+      <c r="AU45" s="40"/>
+      <c r="AV45" s="40"/>
+      <c r="AW45" s="40"/>
+      <c r="AX45" s="40"/>
+      <c r="AY45" s="40"/>
+      <c r="AZ45" s="40"/>
+      <c r="BA45" s="40"/>
+      <c r="BB45" s="40"/>
+      <c r="BC45" s="40"/>
+      <c r="BD45" s="40"/>
+      <c r="BE45" s="40"/>
+      <c r="BF45" s="40"/>
+      <c r="BG45" s="40"/>
+      <c r="BH45" s="40"/>
+      <c r="BI45" s="41"/>
+      <c r="BJ45" s="46"/>
+      <c r="BK45" s="46"/>
+      <c r="BL45" s="46"/>
+      <c r="BM45" s="46"/>
+      <c r="BN45" s="46"/>
+      <c r="BO45" s="46"/>
+      <c r="BP45" s="46"/>
+      <c r="BQ45" s="46"/>
+      <c r="BR45" s="46"/>
+      <c r="BS45" s="46"/>
+      <c r="BT45" s="46"/>
+      <c r="BU45" s="46"/>
+      <c r="BV45" s="46"/>
+      <c r="BW45" s="46"/>
+      <c r="BX45" s="46"/>
+      <c r="BY45" s="46"/>
+      <c r="BZ45" s="46"/>
+      <c r="CA45" s="46"/>
+      <c r="CB45" s="46"/>
+      <c r="CC45" s="46"/>
+      <c r="CD45" s="46"/>
+      <c r="CE45" s="46"/>
+      <c r="CF45" s="46"/>
+      <c r="CG45" s="46"/>
+      <c r="CH45" s="46"/>
+      <c r="CI45" s="46"/>
+      <c r="CJ45" s="46"/>
+      <c r="CK45" s="46"/>
+      <c r="CL45" s="46"/>
+      <c r="CM45" s="46"/>
+      <c r="CN45" s="46"/>
+      <c r="CO45" s="46"/>
+      <c r="CP45" s="46"/>
+      <c r="CQ45" s="46"/>
+      <c r="CR45" s="46"/>
+      <c r="CS45" s="46"/>
+      <c r="CT45" s="46"/>
+      <c r="CU45" s="46"/>
+      <c r="CV45" s="46"/>
+      <c r="CW45" s="46"/>
+      <c r="CX45" s="46"/>
+      <c r="CY45" s="46"/>
+      <c r="CZ45" s="46"/>
+      <c r="DA45" s="46"/>
+      <c r="DB45" s="46"/>
+      <c r="DC45" s="46"/>
+      <c r="DD45" s="46"/>
+      <c r="DE45" s="46"/>
+      <c r="DF45" s="46"/>
+      <c r="DG45" s="46"/>
+      <c r="DH45" s="46"/>
+      <c r="DI45" s="46"/>
+      <c r="DJ45" s="46"/>
+      <c r="DK45" s="46"/>
+      <c r="DL45" s="46"/>
+      <c r="DM45" s="46"/>
+      <c r="DN45" s="46"/>
+      <c r="DO45" s="46"/>
+      <c r="DP45" s="46"/>
+      <c r="DQ45" s="46"/>
+      <c r="DR45" s="46"/>
+      <c r="DS45" s="46"/>
+      <c r="DT45" s="46"/>
+      <c r="DU45" s="46"/>
+      <c r="DV45" s="46"/>
+      <c r="DW45" s="46"/>
+      <c r="DX45" s="46"/>
+      <c r="DY45" s="46"/>
+      <c r="DZ45" s="46"/>
+      <c r="EA45" s="46"/>
+      <c r="EB45" s="46"/>
+      <c r="EC45" s="46"/>
+      <c r="ED45" s="46"/>
+      <c r="EE45" s="46"/>
+      <c r="EF45" s="46"/>
+      <c r="EG45" s="46"/>
+      <c r="EH45" s="46"/>
+      <c r="EI45" s="46"/>
+      <c r="EJ45" s="46"/>
+      <c r="EK45" s="46"/>
+      <c r="EL45" s="46"/>
+      <c r="EM45" s="46"/>
+      <c r="EN45" s="46"/>
+      <c r="EO45" s="46"/>
+      <c r="EP45" s="46"/>
+      <c r="EQ45" s="46"/>
+      <c r="ER45" s="46"/>
+      <c r="ES45" s="46"/>
+      <c r="ET45" s="46"/>
+      <c r="EU45" s="46"/>
+      <c r="EV45" s="46"/>
+      <c r="EW45" s="46"/>
+      <c r="EX45" s="46"/>
+      <c r="EY45" s="46"/>
+      <c r="EZ45" s="46"/>
+      <c r="FA45" s="46"/>
+      <c r="FB45" s="46"/>
+      <c r="FC45" s="46"/>
+      <c r="FD45" s="46"/>
+      <c r="FE45" s="46"/>
+      <c r="FF45" s="46"/>
+      <c r="FG45" s="46"/>
+      <c r="FH45" s="46"/>
+      <c r="FI45" s="46"/>
+      <c r="FJ45" s="46"/>
+      <c r="FK45" s="46"/>
+      <c r="FL45" s="46"/>
+      <c r="FM45" s="46"/>
+      <c r="FN45" s="46"/>
+      <c r="FO45" s="46"/>
+      <c r="FP45" s="46"/>
+      <c r="FQ45" s="46"/>
+      <c r="FR45" s="46"/>
+      <c r="FS45" s="46"/>
+      <c r="FT45" s="46"/>
+      <c r="FU45" s="46"/>
+      <c r="FV45" s="46"/>
+      <c r="FW45" s="46"/>
+      <c r="FX45" s="46"/>
+      <c r="FY45" s="46"/>
+      <c r="FZ45" s="46"/>
+      <c r="GA45" s="46"/>
+      <c r="GB45" s="46"/>
+      <c r="GC45" s="46"/>
+      <c r="GD45" s="46"/>
+      <c r="GE45" s="46"/>
+      <c r="GF45" s="46"/>
+      <c r="GG45" s="46"/>
+      <c r="GH45" s="46"/>
+      <c r="GI45" s="46"/>
+      <c r="GJ45" s="46"/>
+      <c r="GK45" s="46"/>
+      <c r="GL45" s="46"/>
+      <c r="GM45" s="46"/>
+      <c r="GN45" s="46"/>
+      <c r="GO45" s="46"/>
+      <c r="GP45" s="46"/>
+      <c r="GQ45" s="46"/>
+      <c r="GR45" s="46"/>
+      <c r="GS45" s="46"/>
+      <c r="GT45" s="46"/>
+      <c r="GU45" s="46"/>
+      <c r="GV45" s="46"/>
+      <c r="GW45" s="46"/>
+      <c r="GX45" s="46"/>
+      <c r="GY45" s="46"/>
+      <c r="GZ45" s="46"/>
+      <c r="HA45" s="46"/>
+      <c r="HB45" s="46"/>
+      <c r="HC45" s="46"/>
+      <c r="HD45" s="46"/>
+      <c r="HE45" s="46"/>
+      <c r="HF45" s="46"/>
+      <c r="HG45" s="46"/>
+      <c r="HH45" s="46"/>
+      <c r="HI45" s="46"/>
+      <c r="HJ45" s="46"/>
+      <c r="HK45" s="46"/>
+      <c r="HL45" s="46"/>
+      <c r="HM45" s="46"/>
+      <c r="HN45" s="46"/>
+      <c r="HO45" s="46"/>
+      <c r="HP45" s="46"/>
+      <c r="HQ45" s="46"/>
+      <c r="HR45" s="46"/>
+      <c r="HS45" s="46"/>
+      <c r="HT45" s="46"/>
+      <c r="HU45" s="46"/>
+      <c r="HV45" s="46"/>
+      <c r="HW45" s="46"/>
+      <c r="HX45" s="46"/>
+      <c r="HY45" s="46"/>
+      <c r="HZ45" s="46"/>
+      <c r="IA45" s="46"/>
+      <c r="IB45" s="46"/>
+      <c r="IC45" s="46"/>
+      <c r="ID45" s="46"/>
+      <c r="IE45" s="46"/>
+      <c r="IF45" s="46"/>
+      <c r="IG45" s="46"/>
+      <c r="IH45" s="46"/>
+      <c r="II45" s="46"/>
+      <c r="IJ45" s="46"/>
+      <c r="IK45" s="46"/>
+      <c r="IL45" s="46"/>
+      <c r="IM45" s="46"/>
+      <c r="IN45" s="46"/>
+      <c r="IO45" s="46"/>
+      <c r="IP45" s="46"/>
+      <c r="IQ45" s="46"/>
+      <c r="IR45" s="46"/>
+      <c r="IS45" s="46"/>
+      <c r="IT45" s="46"/>
+      <c r="IU45" s="46"/>
+      <c r="IV45" s="46"/>
+      <c r="IW45" s="46"/>
+      <c r="IX45" s="46"/>
     </row>
     <row r="46" spans="1:258" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
@@ -14482,7 +14450,7 @@
       <c r="N46" s="12"/>
       <c r="O46" s="13"/>
       <c r="P46" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="T46" s="15"/>
       <c r="U46" s="15"/>
@@ -14526,203 +14494,203 @@
       <c r="BG46" s="12"/>
       <c r="BH46" s="12"/>
       <c r="BI46" s="13"/>
-      <c r="BJ46" s="67"/>
-      <c r="BK46" s="67"/>
-      <c r="BL46" s="67"/>
-      <c r="BM46" s="67"/>
-      <c r="BN46" s="67"/>
-      <c r="BO46" s="67"/>
-      <c r="BP46" s="67"/>
-      <c r="BQ46" s="67"/>
-      <c r="BR46" s="67"/>
-      <c r="BS46" s="67"/>
-      <c r="BT46" s="67"/>
-      <c r="BU46" s="67"/>
-      <c r="BV46" s="67"/>
-      <c r="BW46" s="67"/>
-      <c r="BX46" s="67"/>
-      <c r="BY46" s="67"/>
-      <c r="BZ46" s="67"/>
-      <c r="CA46" s="67"/>
-      <c r="CB46" s="67"/>
-      <c r="CC46" s="67"/>
-      <c r="CD46" s="67"/>
-      <c r="CE46" s="67"/>
-      <c r="CF46" s="67"/>
-      <c r="CG46" s="67"/>
-      <c r="CH46" s="67"/>
-      <c r="CI46" s="67"/>
-      <c r="CJ46" s="67"/>
-      <c r="CK46" s="67"/>
-      <c r="CL46" s="67"/>
-      <c r="CM46" s="67"/>
-      <c r="CN46" s="67"/>
-      <c r="CO46" s="67"/>
-      <c r="CP46" s="67"/>
-      <c r="CQ46" s="67"/>
-      <c r="CR46" s="67"/>
-      <c r="CS46" s="67"/>
-      <c r="CT46" s="67"/>
-      <c r="CU46" s="67"/>
-      <c r="CV46" s="67"/>
-      <c r="CW46" s="67"/>
-      <c r="CX46" s="67"/>
-      <c r="CY46" s="67"/>
-      <c r="CZ46" s="67"/>
-      <c r="DA46" s="67"/>
-      <c r="DB46" s="67"/>
-      <c r="DC46" s="67"/>
-      <c r="DD46" s="67"/>
-      <c r="DE46" s="67"/>
-      <c r="DF46" s="67"/>
-      <c r="DG46" s="67"/>
-      <c r="DH46" s="67"/>
-      <c r="DI46" s="67"/>
-      <c r="DJ46" s="67"/>
-      <c r="DK46" s="67"/>
-      <c r="DL46" s="67"/>
-      <c r="DM46" s="67"/>
-      <c r="DN46" s="67"/>
-      <c r="DO46" s="67"/>
-      <c r="DP46" s="67"/>
-      <c r="DQ46" s="67"/>
-      <c r="DR46" s="67"/>
-      <c r="DS46" s="67"/>
-      <c r="DT46" s="67"/>
-      <c r="DU46" s="67"/>
-      <c r="DV46" s="67"/>
-      <c r="DW46" s="67"/>
-      <c r="DX46" s="67"/>
-      <c r="DY46" s="67"/>
-      <c r="DZ46" s="67"/>
-      <c r="EA46" s="67"/>
-      <c r="EB46" s="67"/>
-      <c r="EC46" s="67"/>
-      <c r="ED46" s="67"/>
-      <c r="EE46" s="67"/>
-      <c r="EF46" s="67"/>
-      <c r="EG46" s="67"/>
-      <c r="EH46" s="67"/>
-      <c r="EI46" s="67"/>
-      <c r="EJ46" s="67"/>
-      <c r="EK46" s="67"/>
-      <c r="EL46" s="67"/>
-      <c r="EM46" s="67"/>
-      <c r="EN46" s="67"/>
-      <c r="EO46" s="67"/>
-      <c r="EP46" s="67"/>
-      <c r="EQ46" s="67"/>
-      <c r="ER46" s="67"/>
-      <c r="ES46" s="67"/>
-      <c r="ET46" s="67"/>
-      <c r="EU46" s="67"/>
-      <c r="EV46" s="67"/>
-      <c r="EW46" s="67"/>
-      <c r="EX46" s="67"/>
-      <c r="EY46" s="67"/>
-      <c r="EZ46" s="67"/>
-      <c r="FA46" s="67"/>
-      <c r="FB46" s="67"/>
-      <c r="FC46" s="67"/>
-      <c r="FD46" s="67"/>
-      <c r="FE46" s="67"/>
-      <c r="FF46" s="67"/>
-      <c r="FG46" s="67"/>
-      <c r="FH46" s="67"/>
-      <c r="FI46" s="67"/>
-      <c r="FJ46" s="67"/>
-      <c r="FK46" s="67"/>
-      <c r="FL46" s="67"/>
-      <c r="FM46" s="67"/>
-      <c r="FN46" s="67"/>
-      <c r="FO46" s="67"/>
-      <c r="FP46" s="67"/>
-      <c r="FQ46" s="67"/>
-      <c r="FR46" s="67"/>
-      <c r="FS46" s="67"/>
-      <c r="FT46" s="67"/>
-      <c r="FU46" s="67"/>
-      <c r="FV46" s="67"/>
-      <c r="FW46" s="67"/>
-      <c r="FX46" s="67"/>
-      <c r="FY46" s="67"/>
-      <c r="FZ46" s="67"/>
-      <c r="GA46" s="67"/>
-      <c r="GB46" s="67"/>
-      <c r="GC46" s="67"/>
-      <c r="GD46" s="67"/>
-      <c r="GE46" s="67"/>
-      <c r="GF46" s="67"/>
-      <c r="GG46" s="67"/>
-      <c r="GH46" s="67"/>
-      <c r="GI46" s="67"/>
-      <c r="GJ46" s="67"/>
-      <c r="GK46" s="67"/>
-      <c r="GL46" s="67"/>
-      <c r="GM46" s="67"/>
-      <c r="GN46" s="67"/>
-      <c r="GO46" s="67"/>
-      <c r="GP46" s="67"/>
-      <c r="GQ46" s="67"/>
-      <c r="GR46" s="67"/>
-      <c r="GS46" s="67"/>
-      <c r="GT46" s="67"/>
-      <c r="GU46" s="67"/>
-      <c r="GV46" s="67"/>
-      <c r="GW46" s="67"/>
-      <c r="GX46" s="67"/>
-      <c r="GY46" s="67"/>
-      <c r="GZ46" s="67"/>
-      <c r="HA46" s="67"/>
-      <c r="HB46" s="67"/>
-      <c r="HC46" s="67"/>
-      <c r="HD46" s="67"/>
-      <c r="HE46" s="67"/>
-      <c r="HF46" s="67"/>
-      <c r="HG46" s="67"/>
-      <c r="HH46" s="67"/>
-      <c r="HI46" s="67"/>
-      <c r="HJ46" s="67"/>
-      <c r="HK46" s="67"/>
-      <c r="HL46" s="67"/>
-      <c r="HM46" s="67"/>
-      <c r="HN46" s="67"/>
-      <c r="HO46" s="67"/>
-      <c r="HP46" s="67"/>
-      <c r="HQ46" s="67"/>
-      <c r="HR46" s="67"/>
-      <c r="HS46" s="67"/>
-      <c r="HT46" s="67"/>
-      <c r="HU46" s="67"/>
-      <c r="HV46" s="67"/>
-      <c r="HW46" s="67"/>
-      <c r="HX46" s="67"/>
-      <c r="HY46" s="67"/>
-      <c r="HZ46" s="67"/>
-      <c r="IA46" s="67"/>
-      <c r="IB46" s="67"/>
-      <c r="IC46" s="67"/>
-      <c r="ID46" s="67"/>
-      <c r="IE46" s="67"/>
-      <c r="IF46" s="67"/>
-      <c r="IG46" s="67"/>
-      <c r="IH46" s="67"/>
-      <c r="II46" s="67"/>
-      <c r="IJ46" s="67"/>
-      <c r="IK46" s="67"/>
-      <c r="IL46" s="67"/>
-      <c r="IM46" s="67"/>
-      <c r="IN46" s="67"/>
-      <c r="IO46" s="67"/>
-      <c r="IP46" s="67"/>
-      <c r="IQ46" s="67"/>
-      <c r="IR46" s="67"/>
-      <c r="IS46" s="67"/>
-      <c r="IT46" s="67"/>
-      <c r="IU46" s="67"/>
-      <c r="IV46" s="67"/>
-      <c r="IW46" s="67"/>
-      <c r="IX46" s="67"/>
+      <c r="BJ46" s="47"/>
+      <c r="BK46" s="47"/>
+      <c r="BL46" s="47"/>
+      <c r="BM46" s="47"/>
+      <c r="BN46" s="47"/>
+      <c r="BO46" s="47"/>
+      <c r="BP46" s="47"/>
+      <c r="BQ46" s="47"/>
+      <c r="BR46" s="47"/>
+      <c r="BS46" s="47"/>
+      <c r="BT46" s="47"/>
+      <c r="BU46" s="47"/>
+      <c r="BV46" s="47"/>
+      <c r="BW46" s="47"/>
+      <c r="BX46" s="47"/>
+      <c r="BY46" s="47"/>
+      <c r="BZ46" s="47"/>
+      <c r="CA46" s="47"/>
+      <c r="CB46" s="47"/>
+      <c r="CC46" s="47"/>
+      <c r="CD46" s="47"/>
+      <c r="CE46" s="47"/>
+      <c r="CF46" s="47"/>
+      <c r="CG46" s="47"/>
+      <c r="CH46" s="47"/>
+      <c r="CI46" s="47"/>
+      <c r="CJ46" s="47"/>
+      <c r="CK46" s="47"/>
+      <c r="CL46" s="47"/>
+      <c r="CM46" s="47"/>
+      <c r="CN46" s="47"/>
+      <c r="CO46" s="47"/>
+      <c r="CP46" s="47"/>
+      <c r="CQ46" s="47"/>
+      <c r="CR46" s="47"/>
+      <c r="CS46" s="47"/>
+      <c r="CT46" s="47"/>
+      <c r="CU46" s="47"/>
+      <c r="CV46" s="47"/>
+      <c r="CW46" s="47"/>
+      <c r="CX46" s="47"/>
+      <c r="CY46" s="47"/>
+      <c r="CZ46" s="47"/>
+      <c r="DA46" s="47"/>
+      <c r="DB46" s="47"/>
+      <c r="DC46" s="47"/>
+      <c r="DD46" s="47"/>
+      <c r="DE46" s="47"/>
+      <c r="DF46" s="47"/>
+      <c r="DG46" s="47"/>
+      <c r="DH46" s="47"/>
+      <c r="DI46" s="47"/>
+      <c r="DJ46" s="47"/>
+      <c r="DK46" s="47"/>
+      <c r="DL46" s="47"/>
+      <c r="DM46" s="47"/>
+      <c r="DN46" s="47"/>
+      <c r="DO46" s="47"/>
+      <c r="DP46" s="47"/>
+      <c r="DQ46" s="47"/>
+      <c r="DR46" s="47"/>
+      <c r="DS46" s="47"/>
+      <c r="DT46" s="47"/>
+      <c r="DU46" s="47"/>
+      <c r="DV46" s="47"/>
+      <c r="DW46" s="47"/>
+      <c r="DX46" s="47"/>
+      <c r="DY46" s="47"/>
+      <c r="DZ46" s="47"/>
+      <c r="EA46" s="47"/>
+      <c r="EB46" s="47"/>
+      <c r="EC46" s="47"/>
+      <c r="ED46" s="47"/>
+      <c r="EE46" s="47"/>
+      <c r="EF46" s="47"/>
+      <c r="EG46" s="47"/>
+      <c r="EH46" s="47"/>
+      <c r="EI46" s="47"/>
+      <c r="EJ46" s="47"/>
+      <c r="EK46" s="47"/>
+      <c r="EL46" s="47"/>
+      <c r="EM46" s="47"/>
+      <c r="EN46" s="47"/>
+      <c r="EO46" s="47"/>
+      <c r="EP46" s="47"/>
+      <c r="EQ46" s="47"/>
+      <c r="ER46" s="47"/>
+      <c r="ES46" s="47"/>
+      <c r="ET46" s="47"/>
+      <c r="EU46" s="47"/>
+      <c r="EV46" s="47"/>
+      <c r="EW46" s="47"/>
+      <c r="EX46" s="47"/>
+      <c r="EY46" s="47"/>
+      <c r="EZ46" s="47"/>
+      <c r="FA46" s="47"/>
+      <c r="FB46" s="47"/>
+      <c r="FC46" s="47"/>
+      <c r="FD46" s="47"/>
+      <c r="FE46" s="47"/>
+      <c r="FF46" s="47"/>
+      <c r="FG46" s="47"/>
+      <c r="FH46" s="47"/>
+      <c r="FI46" s="47"/>
+      <c r="FJ46" s="47"/>
+      <c r="FK46" s="47"/>
+      <c r="FL46" s="47"/>
+      <c r="FM46" s="47"/>
+      <c r="FN46" s="47"/>
+      <c r="FO46" s="47"/>
+      <c r="FP46" s="47"/>
+      <c r="FQ46" s="47"/>
+      <c r="FR46" s="47"/>
+      <c r="FS46" s="47"/>
+      <c r="FT46" s="47"/>
+      <c r="FU46" s="47"/>
+      <c r="FV46" s="47"/>
+      <c r="FW46" s="47"/>
+      <c r="FX46" s="47"/>
+      <c r="FY46" s="47"/>
+      <c r="FZ46" s="47"/>
+      <c r="GA46" s="47"/>
+      <c r="GB46" s="47"/>
+      <c r="GC46" s="47"/>
+      <c r="GD46" s="47"/>
+      <c r="GE46" s="47"/>
+      <c r="GF46" s="47"/>
+      <c r="GG46" s="47"/>
+      <c r="GH46" s="47"/>
+      <c r="GI46" s="47"/>
+      <c r="GJ46" s="47"/>
+      <c r="GK46" s="47"/>
+      <c r="GL46" s="47"/>
+      <c r="GM46" s="47"/>
+      <c r="GN46" s="47"/>
+      <c r="GO46" s="47"/>
+      <c r="GP46" s="47"/>
+      <c r="GQ46" s="47"/>
+      <c r="GR46" s="47"/>
+      <c r="GS46" s="47"/>
+      <c r="GT46" s="47"/>
+      <c r="GU46" s="47"/>
+      <c r="GV46" s="47"/>
+      <c r="GW46" s="47"/>
+      <c r="GX46" s="47"/>
+      <c r="GY46" s="47"/>
+      <c r="GZ46" s="47"/>
+      <c r="HA46" s="47"/>
+      <c r="HB46" s="47"/>
+      <c r="HC46" s="47"/>
+      <c r="HD46" s="47"/>
+      <c r="HE46" s="47"/>
+      <c r="HF46" s="47"/>
+      <c r="HG46" s="47"/>
+      <c r="HH46" s="47"/>
+      <c r="HI46" s="47"/>
+      <c r="HJ46" s="47"/>
+      <c r="HK46" s="47"/>
+      <c r="HL46" s="47"/>
+      <c r="HM46" s="47"/>
+      <c r="HN46" s="47"/>
+      <c r="HO46" s="47"/>
+      <c r="HP46" s="47"/>
+      <c r="HQ46" s="47"/>
+      <c r="HR46" s="47"/>
+      <c r="HS46" s="47"/>
+      <c r="HT46" s="47"/>
+      <c r="HU46" s="47"/>
+      <c r="HV46" s="47"/>
+      <c r="HW46" s="47"/>
+      <c r="HX46" s="47"/>
+      <c r="HY46" s="47"/>
+      <c r="HZ46" s="47"/>
+      <c r="IA46" s="47"/>
+      <c r="IB46" s="47"/>
+      <c r="IC46" s="47"/>
+      <c r="ID46" s="47"/>
+      <c r="IE46" s="47"/>
+      <c r="IF46" s="47"/>
+      <c r="IG46" s="47"/>
+      <c r="IH46" s="47"/>
+      <c r="II46" s="47"/>
+      <c r="IJ46" s="47"/>
+      <c r="IK46" s="47"/>
+      <c r="IL46" s="47"/>
+      <c r="IM46" s="47"/>
+      <c r="IN46" s="47"/>
+      <c r="IO46" s="47"/>
+      <c r="IP46" s="47"/>
+      <c r="IQ46" s="47"/>
+      <c r="IR46" s="47"/>
+      <c r="IS46" s="47"/>
+      <c r="IT46" s="47"/>
+      <c r="IU46" s="47"/>
+      <c r="IV46" s="47"/>
+      <c r="IW46" s="47"/>
+      <c r="IX46" s="47"/>
     </row>
     <row r="47" spans="1:258" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
@@ -14740,12 +14708,12 @@
       <c r="M47" s="12"/>
       <c r="N47" s="12"/>
       <c r="O47" s="12"/>
-      <c r="P47" s="68"/>
-      <c r="Q47" s="58" t="s">
-        <v>77</v>
+      <c r="P47" s="48"/>
+      <c r="Q47" s="38" t="s">
+        <v>73</v>
       </c>
-      <c r="R47" s="58"/>
-      <c r="S47" s="58"/>
+      <c r="R47" s="38"/>
+      <c r="S47" s="38"/>
       <c r="T47" s="15"/>
       <c r="U47" s="15"/>
       <c r="V47" s="15"/>
@@ -14788,203 +14756,203 @@
       <c r="BG47" s="12"/>
       <c r="BH47" s="12"/>
       <c r="BI47" s="13"/>
-      <c r="BJ47" s="67"/>
-      <c r="BK47" s="67"/>
-      <c r="BL47" s="67"/>
-      <c r="BM47" s="67"/>
-      <c r="BN47" s="67"/>
-      <c r="BO47" s="67"/>
-      <c r="BP47" s="67"/>
-      <c r="BQ47" s="67"/>
-      <c r="BR47" s="67"/>
-      <c r="BS47" s="67"/>
-      <c r="BT47" s="67"/>
-      <c r="BU47" s="67"/>
-      <c r="BV47" s="67"/>
-      <c r="BW47" s="67"/>
-      <c r="BX47" s="67"/>
-      <c r="BY47" s="67"/>
-      <c r="BZ47" s="67"/>
-      <c r="CA47" s="67"/>
-      <c r="CB47" s="67"/>
-      <c r="CC47" s="67"/>
-      <c r="CD47" s="67"/>
-      <c r="CE47" s="67"/>
-      <c r="CF47" s="67"/>
-      <c r="CG47" s="67"/>
-      <c r="CH47" s="67"/>
-      <c r="CI47" s="67"/>
-      <c r="CJ47" s="67"/>
-      <c r="CK47" s="67"/>
-      <c r="CL47" s="67"/>
-      <c r="CM47" s="67"/>
-      <c r="CN47" s="67"/>
-      <c r="CO47" s="67"/>
-      <c r="CP47" s="67"/>
-      <c r="CQ47" s="67"/>
-      <c r="CR47" s="67"/>
-      <c r="CS47" s="67"/>
-      <c r="CT47" s="67"/>
-      <c r="CU47" s="67"/>
-      <c r="CV47" s="67"/>
-      <c r="CW47" s="67"/>
-      <c r="CX47" s="67"/>
-      <c r="CY47" s="67"/>
-      <c r="CZ47" s="67"/>
-      <c r="DA47" s="67"/>
-      <c r="DB47" s="67"/>
-      <c r="DC47" s="67"/>
-      <c r="DD47" s="67"/>
-      <c r="DE47" s="67"/>
-      <c r="DF47" s="67"/>
-      <c r="DG47" s="67"/>
-      <c r="DH47" s="67"/>
-      <c r="DI47" s="67"/>
-      <c r="DJ47" s="67"/>
-      <c r="DK47" s="67"/>
-      <c r="DL47" s="67"/>
-      <c r="DM47" s="67"/>
-      <c r="DN47" s="67"/>
-      <c r="DO47" s="67"/>
-      <c r="DP47" s="67"/>
-      <c r="DQ47" s="67"/>
-      <c r="DR47" s="67"/>
-      <c r="DS47" s="67"/>
-      <c r="DT47" s="67"/>
-      <c r="DU47" s="67"/>
-      <c r="DV47" s="67"/>
-      <c r="DW47" s="67"/>
-      <c r="DX47" s="67"/>
-      <c r="DY47" s="67"/>
-      <c r="DZ47" s="67"/>
-      <c r="EA47" s="67"/>
-      <c r="EB47" s="67"/>
-      <c r="EC47" s="67"/>
-      <c r="ED47" s="67"/>
-      <c r="EE47" s="67"/>
-      <c r="EF47" s="67"/>
-      <c r="EG47" s="67"/>
-      <c r="EH47" s="67"/>
-      <c r="EI47" s="67"/>
-      <c r="EJ47" s="67"/>
-      <c r="EK47" s="67"/>
-      <c r="EL47" s="67"/>
-      <c r="EM47" s="67"/>
-      <c r="EN47" s="67"/>
-      <c r="EO47" s="67"/>
-      <c r="EP47" s="67"/>
-      <c r="EQ47" s="67"/>
-      <c r="ER47" s="67"/>
-      <c r="ES47" s="67"/>
-      <c r="ET47" s="67"/>
-      <c r="EU47" s="67"/>
-      <c r="EV47" s="67"/>
-      <c r="EW47" s="67"/>
-      <c r="EX47" s="67"/>
-      <c r="EY47" s="67"/>
-      <c r="EZ47" s="67"/>
-      <c r="FA47" s="67"/>
-      <c r="FB47" s="67"/>
-      <c r="FC47" s="67"/>
-      <c r="FD47" s="67"/>
-      <c r="FE47" s="67"/>
-      <c r="FF47" s="67"/>
-      <c r="FG47" s="67"/>
-      <c r="FH47" s="67"/>
-      <c r="FI47" s="67"/>
-      <c r="FJ47" s="67"/>
-      <c r="FK47" s="67"/>
-      <c r="FL47" s="67"/>
-      <c r="FM47" s="67"/>
-      <c r="FN47" s="67"/>
-      <c r="FO47" s="67"/>
-      <c r="FP47" s="67"/>
-      <c r="FQ47" s="67"/>
-      <c r="FR47" s="67"/>
-      <c r="FS47" s="67"/>
-      <c r="FT47" s="67"/>
-      <c r="FU47" s="67"/>
-      <c r="FV47" s="67"/>
-      <c r="FW47" s="67"/>
-      <c r="FX47" s="67"/>
-      <c r="FY47" s="67"/>
-      <c r="FZ47" s="67"/>
-      <c r="GA47" s="67"/>
-      <c r="GB47" s="67"/>
-      <c r="GC47" s="67"/>
-      <c r="GD47" s="67"/>
-      <c r="GE47" s="67"/>
-      <c r="GF47" s="67"/>
-      <c r="GG47" s="67"/>
-      <c r="GH47" s="67"/>
-      <c r="GI47" s="67"/>
-      <c r="GJ47" s="67"/>
-      <c r="GK47" s="67"/>
-      <c r="GL47" s="67"/>
-      <c r="GM47" s="67"/>
-      <c r="GN47" s="67"/>
-      <c r="GO47" s="67"/>
-      <c r="GP47" s="67"/>
-      <c r="GQ47" s="67"/>
-      <c r="GR47" s="67"/>
-      <c r="GS47" s="67"/>
-      <c r="GT47" s="67"/>
-      <c r="GU47" s="67"/>
-      <c r="GV47" s="67"/>
-      <c r="GW47" s="67"/>
-      <c r="GX47" s="67"/>
-      <c r="GY47" s="67"/>
-      <c r="GZ47" s="67"/>
-      <c r="HA47" s="67"/>
-      <c r="HB47" s="67"/>
-      <c r="HC47" s="67"/>
-      <c r="HD47" s="67"/>
-      <c r="HE47" s="67"/>
-      <c r="HF47" s="67"/>
-      <c r="HG47" s="67"/>
-      <c r="HH47" s="67"/>
-      <c r="HI47" s="67"/>
-      <c r="HJ47" s="67"/>
-      <c r="HK47" s="67"/>
-      <c r="HL47" s="67"/>
-      <c r="HM47" s="67"/>
-      <c r="HN47" s="67"/>
-      <c r="HO47" s="67"/>
-      <c r="HP47" s="67"/>
-      <c r="HQ47" s="67"/>
-      <c r="HR47" s="67"/>
-      <c r="HS47" s="67"/>
-      <c r="HT47" s="67"/>
-      <c r="HU47" s="67"/>
-      <c r="HV47" s="67"/>
-      <c r="HW47" s="67"/>
-      <c r="HX47" s="67"/>
-      <c r="HY47" s="67"/>
-      <c r="HZ47" s="67"/>
-      <c r="IA47" s="67"/>
-      <c r="IB47" s="67"/>
-      <c r="IC47" s="67"/>
-      <c r="ID47" s="67"/>
-      <c r="IE47" s="67"/>
-      <c r="IF47" s="67"/>
-      <c r="IG47" s="67"/>
-      <c r="IH47" s="67"/>
-      <c r="II47" s="67"/>
-      <c r="IJ47" s="67"/>
-      <c r="IK47" s="67"/>
-      <c r="IL47" s="67"/>
-      <c r="IM47" s="67"/>
-      <c r="IN47" s="67"/>
-      <c r="IO47" s="67"/>
-      <c r="IP47" s="67"/>
-      <c r="IQ47" s="67"/>
-      <c r="IR47" s="67"/>
-      <c r="IS47" s="67"/>
-      <c r="IT47" s="67"/>
-      <c r="IU47" s="67"/>
-      <c r="IV47" s="67"/>
-      <c r="IW47" s="67"/>
-      <c r="IX47" s="67"/>
+      <c r="BJ47" s="47"/>
+      <c r="BK47" s="47"/>
+      <c r="BL47" s="47"/>
+      <c r="BM47" s="47"/>
+      <c r="BN47" s="47"/>
+      <c r="BO47" s="47"/>
+      <c r="BP47" s="47"/>
+      <c r="BQ47" s="47"/>
+      <c r="BR47" s="47"/>
+      <c r="BS47" s="47"/>
+      <c r="BT47" s="47"/>
+      <c r="BU47" s="47"/>
+      <c r="BV47" s="47"/>
+      <c r="BW47" s="47"/>
+      <c r="BX47" s="47"/>
+      <c r="BY47" s="47"/>
+      <c r="BZ47" s="47"/>
+      <c r="CA47" s="47"/>
+      <c r="CB47" s="47"/>
+      <c r="CC47" s="47"/>
+      <c r="CD47" s="47"/>
+      <c r="CE47" s="47"/>
+      <c r="CF47" s="47"/>
+      <c r="CG47" s="47"/>
+      <c r="CH47" s="47"/>
+      <c r="CI47" s="47"/>
+      <c r="CJ47" s="47"/>
+      <c r="CK47" s="47"/>
+      <c r="CL47" s="47"/>
+      <c r="CM47" s="47"/>
+      <c r="CN47" s="47"/>
+      <c r="CO47" s="47"/>
+      <c r="CP47" s="47"/>
+      <c r="CQ47" s="47"/>
+      <c r="CR47" s="47"/>
+      <c r="CS47" s="47"/>
+      <c r="CT47" s="47"/>
+      <c r="CU47" s="47"/>
+      <c r="CV47" s="47"/>
+      <c r="CW47" s="47"/>
+      <c r="CX47" s="47"/>
+      <c r="CY47" s="47"/>
+      <c r="CZ47" s="47"/>
+      <c r="DA47" s="47"/>
+      <c r="DB47" s="47"/>
+      <c r="DC47" s="47"/>
+      <c r="DD47" s="47"/>
+      <c r="DE47" s="47"/>
+      <c r="DF47" s="47"/>
+      <c r="DG47" s="47"/>
+      <c r="DH47" s="47"/>
+      <c r="DI47" s="47"/>
+      <c r="DJ47" s="47"/>
+      <c r="DK47" s="47"/>
+      <c r="DL47" s="47"/>
+      <c r="DM47" s="47"/>
+      <c r="DN47" s="47"/>
+      <c r="DO47" s="47"/>
+      <c r="DP47" s="47"/>
+      <c r="DQ47" s="47"/>
+      <c r="DR47" s="47"/>
+      <c r="DS47" s="47"/>
+      <c r="DT47" s="47"/>
+      <c r="DU47" s="47"/>
+      <c r="DV47" s="47"/>
+      <c r="DW47" s="47"/>
+      <c r="DX47" s="47"/>
+      <c r="DY47" s="47"/>
+      <c r="DZ47" s="47"/>
+      <c r="EA47" s="47"/>
+      <c r="EB47" s="47"/>
+      <c r="EC47" s="47"/>
+      <c r="ED47" s="47"/>
+      <c r="EE47" s="47"/>
+      <c r="EF47" s="47"/>
+      <c r="EG47" s="47"/>
+      <c r="EH47" s="47"/>
+      <c r="EI47" s="47"/>
+      <c r="EJ47" s="47"/>
+      <c r="EK47" s="47"/>
+      <c r="EL47" s="47"/>
+      <c r="EM47" s="47"/>
+      <c r="EN47" s="47"/>
+      <c r="EO47" s="47"/>
+      <c r="EP47" s="47"/>
+      <c r="EQ47" s="47"/>
+      <c r="ER47" s="47"/>
+      <c r="ES47" s="47"/>
+      <c r="ET47" s="47"/>
+      <c r="EU47" s="47"/>
+      <c r="EV47" s="47"/>
+      <c r="EW47" s="47"/>
+      <c r="EX47" s="47"/>
+      <c r="EY47" s="47"/>
+      <c r="EZ47" s="47"/>
+      <c r="FA47" s="47"/>
+      <c r="FB47" s="47"/>
+      <c r="FC47" s="47"/>
+      <c r="FD47" s="47"/>
+      <c r="FE47" s="47"/>
+      <c r="FF47" s="47"/>
+      <c r="FG47" s="47"/>
+      <c r="FH47" s="47"/>
+      <c r="FI47" s="47"/>
+      <c r="FJ47" s="47"/>
+      <c r="FK47" s="47"/>
+      <c r="FL47" s="47"/>
+      <c r="FM47" s="47"/>
+      <c r="FN47" s="47"/>
+      <c r="FO47" s="47"/>
+      <c r="FP47" s="47"/>
+      <c r="FQ47" s="47"/>
+      <c r="FR47" s="47"/>
+      <c r="FS47" s="47"/>
+      <c r="FT47" s="47"/>
+      <c r="FU47" s="47"/>
+      <c r="FV47" s="47"/>
+      <c r="FW47" s="47"/>
+      <c r="FX47" s="47"/>
+      <c r="FY47" s="47"/>
+      <c r="FZ47" s="47"/>
+      <c r="GA47" s="47"/>
+      <c r="GB47" s="47"/>
+      <c r="GC47" s="47"/>
+      <c r="GD47" s="47"/>
+      <c r="GE47" s="47"/>
+      <c r="GF47" s="47"/>
+      <c r="GG47" s="47"/>
+      <c r="GH47" s="47"/>
+      <c r="GI47" s="47"/>
+      <c r="GJ47" s="47"/>
+      <c r="GK47" s="47"/>
+      <c r="GL47" s="47"/>
+      <c r="GM47" s="47"/>
+      <c r="GN47" s="47"/>
+      <c r="GO47" s="47"/>
+      <c r="GP47" s="47"/>
+      <c r="GQ47" s="47"/>
+      <c r="GR47" s="47"/>
+      <c r="GS47" s="47"/>
+      <c r="GT47" s="47"/>
+      <c r="GU47" s="47"/>
+      <c r="GV47" s="47"/>
+      <c r="GW47" s="47"/>
+      <c r="GX47" s="47"/>
+      <c r="GY47" s="47"/>
+      <c r="GZ47" s="47"/>
+      <c r="HA47" s="47"/>
+      <c r="HB47" s="47"/>
+      <c r="HC47" s="47"/>
+      <c r="HD47" s="47"/>
+      <c r="HE47" s="47"/>
+      <c r="HF47" s="47"/>
+      <c r="HG47" s="47"/>
+      <c r="HH47" s="47"/>
+      <c r="HI47" s="47"/>
+      <c r="HJ47" s="47"/>
+      <c r="HK47" s="47"/>
+      <c r="HL47" s="47"/>
+      <c r="HM47" s="47"/>
+      <c r="HN47" s="47"/>
+      <c r="HO47" s="47"/>
+      <c r="HP47" s="47"/>
+      <c r="HQ47" s="47"/>
+      <c r="HR47" s="47"/>
+      <c r="HS47" s="47"/>
+      <c r="HT47" s="47"/>
+      <c r="HU47" s="47"/>
+      <c r="HV47" s="47"/>
+      <c r="HW47" s="47"/>
+      <c r="HX47" s="47"/>
+      <c r="HY47" s="47"/>
+      <c r="HZ47" s="47"/>
+      <c r="IA47" s="47"/>
+      <c r="IB47" s="47"/>
+      <c r="IC47" s="47"/>
+      <c r="ID47" s="47"/>
+      <c r="IE47" s="47"/>
+      <c r="IF47" s="47"/>
+      <c r="IG47" s="47"/>
+      <c r="IH47" s="47"/>
+      <c r="II47" s="47"/>
+      <c r="IJ47" s="47"/>
+      <c r="IK47" s="47"/>
+      <c r="IL47" s="47"/>
+      <c r="IM47" s="47"/>
+      <c r="IN47" s="47"/>
+      <c r="IO47" s="47"/>
+      <c r="IP47" s="47"/>
+      <c r="IQ47" s="47"/>
+      <c r="IR47" s="47"/>
+      <c r="IS47" s="47"/>
+      <c r="IT47" s="47"/>
+      <c r="IU47" s="47"/>
+      <c r="IV47" s="47"/>
+      <c r="IW47" s="47"/>
+      <c r="IX47" s="47"/>
     </row>
     <row r="48" spans="1:258" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
@@ -15003,11 +14971,11 @@
       <c r="N48" s="12"/>
       <c r="O48" s="13"/>
       <c r="P48" s="15"/>
-      <c r="Q48" s="58"/>
-      <c r="R48" s="58" t="s">
-        <v>76</v>
+      <c r="Q48" s="38"/>
+      <c r="R48" s="38" t="s">
+        <v>72</v>
       </c>
-      <c r="S48" s="58"/>
+      <c r="S48" s="38"/>
       <c r="T48" s="15"/>
       <c r="U48" s="15"/>
       <c r="V48" s="15"/>
@@ -15050,203 +15018,203 @@
       <c r="BG48" s="12"/>
       <c r="BH48" s="12"/>
       <c r="BI48" s="13"/>
-      <c r="BJ48" s="67"/>
-      <c r="BK48" s="67"/>
-      <c r="BL48" s="67"/>
-      <c r="BM48" s="67"/>
-      <c r="BN48" s="67"/>
-      <c r="BO48" s="67"/>
-      <c r="BP48" s="67"/>
-      <c r="BQ48" s="67"/>
-      <c r="BR48" s="67"/>
-      <c r="BS48" s="67"/>
-      <c r="BT48" s="67"/>
-      <c r="BU48" s="67"/>
-      <c r="BV48" s="67"/>
-      <c r="BW48" s="67"/>
-      <c r="BX48" s="67"/>
-      <c r="BY48" s="67"/>
-      <c r="BZ48" s="67"/>
-      <c r="CA48" s="67"/>
-      <c r="CB48" s="67"/>
-      <c r="CC48" s="67"/>
-      <c r="CD48" s="67"/>
-      <c r="CE48" s="67"/>
-      <c r="CF48" s="67"/>
-      <c r="CG48" s="67"/>
-      <c r="CH48" s="67"/>
-      <c r="CI48" s="67"/>
-      <c r="CJ48" s="67"/>
-      <c r="CK48" s="67"/>
-      <c r="CL48" s="67"/>
-      <c r="CM48" s="67"/>
-      <c r="CN48" s="67"/>
-      <c r="CO48" s="67"/>
-      <c r="CP48" s="67"/>
-      <c r="CQ48" s="67"/>
-      <c r="CR48" s="67"/>
-      <c r="CS48" s="67"/>
-      <c r="CT48" s="67"/>
-      <c r="CU48" s="67"/>
-      <c r="CV48" s="67"/>
-      <c r="CW48" s="67"/>
-      <c r="CX48" s="67"/>
-      <c r="CY48" s="67"/>
-      <c r="CZ48" s="67"/>
-      <c r="DA48" s="67"/>
-      <c r="DB48" s="67"/>
-      <c r="DC48" s="67"/>
-      <c r="DD48" s="67"/>
-      <c r="DE48" s="67"/>
-      <c r="DF48" s="67"/>
-      <c r="DG48" s="67"/>
-      <c r="DH48" s="67"/>
-      <c r="DI48" s="67"/>
-      <c r="DJ48" s="67"/>
-      <c r="DK48" s="67"/>
-      <c r="DL48" s="67"/>
-      <c r="DM48" s="67"/>
-      <c r="DN48" s="67"/>
-      <c r="DO48" s="67"/>
-      <c r="DP48" s="67"/>
-      <c r="DQ48" s="67"/>
-      <c r="DR48" s="67"/>
-      <c r="DS48" s="67"/>
-      <c r="DT48" s="67"/>
-      <c r="DU48" s="67"/>
-      <c r="DV48" s="67"/>
-      <c r="DW48" s="67"/>
-      <c r="DX48" s="67"/>
-      <c r="DY48" s="67"/>
-      <c r="DZ48" s="67"/>
-      <c r="EA48" s="67"/>
-      <c r="EB48" s="67"/>
-      <c r="EC48" s="67"/>
-      <c r="ED48" s="67"/>
-      <c r="EE48" s="67"/>
-      <c r="EF48" s="67"/>
-      <c r="EG48" s="67"/>
-      <c r="EH48" s="67"/>
-      <c r="EI48" s="67"/>
-      <c r="EJ48" s="67"/>
-      <c r="EK48" s="67"/>
-      <c r="EL48" s="67"/>
-      <c r="EM48" s="67"/>
-      <c r="EN48" s="67"/>
-      <c r="EO48" s="67"/>
-      <c r="EP48" s="67"/>
-      <c r="EQ48" s="67"/>
-      <c r="ER48" s="67"/>
-      <c r="ES48" s="67"/>
-      <c r="ET48" s="67"/>
-      <c r="EU48" s="67"/>
-      <c r="EV48" s="67"/>
-      <c r="EW48" s="67"/>
-      <c r="EX48" s="67"/>
-      <c r="EY48" s="67"/>
-      <c r="EZ48" s="67"/>
-      <c r="FA48" s="67"/>
-      <c r="FB48" s="67"/>
-      <c r="FC48" s="67"/>
-      <c r="FD48" s="67"/>
-      <c r="FE48" s="67"/>
-      <c r="FF48" s="67"/>
-      <c r="FG48" s="67"/>
-      <c r="FH48" s="67"/>
-      <c r="FI48" s="67"/>
-      <c r="FJ48" s="67"/>
-      <c r="FK48" s="67"/>
-      <c r="FL48" s="67"/>
-      <c r="FM48" s="67"/>
-      <c r="FN48" s="67"/>
-      <c r="FO48" s="67"/>
-      <c r="FP48" s="67"/>
-      <c r="FQ48" s="67"/>
-      <c r="FR48" s="67"/>
-      <c r="FS48" s="67"/>
-      <c r="FT48" s="67"/>
-      <c r="FU48" s="67"/>
-      <c r="FV48" s="67"/>
-      <c r="FW48" s="67"/>
-      <c r="FX48" s="67"/>
-      <c r="FY48" s="67"/>
-      <c r="FZ48" s="67"/>
-      <c r="GA48" s="67"/>
-      <c r="GB48" s="67"/>
-      <c r="GC48" s="67"/>
-      <c r="GD48" s="67"/>
-      <c r="GE48" s="67"/>
-      <c r="GF48" s="67"/>
-      <c r="GG48" s="67"/>
-      <c r="GH48" s="67"/>
-      <c r="GI48" s="67"/>
-      <c r="GJ48" s="67"/>
-      <c r="GK48" s="67"/>
-      <c r="GL48" s="67"/>
-      <c r="GM48" s="67"/>
-      <c r="GN48" s="67"/>
-      <c r="GO48" s="67"/>
-      <c r="GP48" s="67"/>
-      <c r="GQ48" s="67"/>
-      <c r="GR48" s="67"/>
-      <c r="GS48" s="67"/>
-      <c r="GT48" s="67"/>
-      <c r="GU48" s="67"/>
-      <c r="GV48" s="67"/>
-      <c r="GW48" s="67"/>
-      <c r="GX48" s="67"/>
-      <c r="GY48" s="67"/>
-      <c r="GZ48" s="67"/>
-      <c r="HA48" s="67"/>
-      <c r="HB48" s="67"/>
-      <c r="HC48" s="67"/>
-      <c r="HD48" s="67"/>
-      <c r="HE48" s="67"/>
-      <c r="HF48" s="67"/>
-      <c r="HG48" s="67"/>
-      <c r="HH48" s="67"/>
-      <c r="HI48" s="67"/>
-      <c r="HJ48" s="67"/>
-      <c r="HK48" s="67"/>
-      <c r="HL48" s="67"/>
-      <c r="HM48" s="67"/>
-      <c r="HN48" s="67"/>
-      <c r="HO48" s="67"/>
-      <c r="HP48" s="67"/>
-      <c r="HQ48" s="67"/>
-      <c r="HR48" s="67"/>
-      <c r="HS48" s="67"/>
-      <c r="HT48" s="67"/>
-      <c r="HU48" s="67"/>
-      <c r="HV48" s="67"/>
-      <c r="HW48" s="67"/>
-      <c r="HX48" s="67"/>
-      <c r="HY48" s="67"/>
-      <c r="HZ48" s="67"/>
-      <c r="IA48" s="67"/>
-      <c r="IB48" s="67"/>
-      <c r="IC48" s="67"/>
-      <c r="ID48" s="67"/>
-      <c r="IE48" s="67"/>
-      <c r="IF48" s="67"/>
-      <c r="IG48" s="67"/>
-      <c r="IH48" s="67"/>
-      <c r="II48" s="67"/>
-      <c r="IJ48" s="67"/>
-      <c r="IK48" s="67"/>
-      <c r="IL48" s="67"/>
-      <c r="IM48" s="67"/>
-      <c r="IN48" s="67"/>
-      <c r="IO48" s="67"/>
-      <c r="IP48" s="67"/>
-      <c r="IQ48" s="67"/>
-      <c r="IR48" s="67"/>
-      <c r="IS48" s="67"/>
-      <c r="IT48" s="67"/>
-      <c r="IU48" s="67"/>
-      <c r="IV48" s="67"/>
-      <c r="IW48" s="67"/>
-      <c r="IX48" s="67"/>
+      <c r="BJ48" s="47"/>
+      <c r="BK48" s="47"/>
+      <c r="BL48" s="47"/>
+      <c r="BM48" s="47"/>
+      <c r="BN48" s="47"/>
+      <c r="BO48" s="47"/>
+      <c r="BP48" s="47"/>
+      <c r="BQ48" s="47"/>
+      <c r="BR48" s="47"/>
+      <c r="BS48" s="47"/>
+      <c r="BT48" s="47"/>
+      <c r="BU48" s="47"/>
+      <c r="BV48" s="47"/>
+      <c r="BW48" s="47"/>
+      <c r="BX48" s="47"/>
+      <c r="BY48" s="47"/>
+      <c r="BZ48" s="47"/>
+      <c r="CA48" s="47"/>
+      <c r="CB48" s="47"/>
+      <c r="CC48" s="47"/>
+      <c r="CD48" s="47"/>
+      <c r="CE48" s="47"/>
+      <c r="CF48" s="47"/>
+      <c r="CG48" s="47"/>
+      <c r="CH48" s="47"/>
+      <c r="CI48" s="47"/>
+      <c r="CJ48" s="47"/>
+      <c r="CK48" s="47"/>
+      <c r="CL48" s="47"/>
+      <c r="CM48" s="47"/>
+      <c r="CN48" s="47"/>
+      <c r="CO48" s="47"/>
+      <c r="CP48" s="47"/>
+      <c r="CQ48" s="47"/>
+      <c r="CR48" s="47"/>
+      <c r="CS48" s="47"/>
+      <c r="CT48" s="47"/>
+      <c r="CU48" s="47"/>
+      <c r="CV48" s="47"/>
+      <c r="CW48" s="47"/>
+      <c r="CX48" s="47"/>
+      <c r="CY48" s="47"/>
+      <c r="CZ48" s="47"/>
+      <c r="DA48" s="47"/>
+      <c r="DB48" s="47"/>
+      <c r="DC48" s="47"/>
+      <c r="DD48" s="47"/>
+      <c r="DE48" s="47"/>
+      <c r="DF48" s="47"/>
+      <c r="DG48" s="47"/>
+      <c r="DH48" s="47"/>
+      <c r="DI48" s="47"/>
+      <c r="DJ48" s="47"/>
+      <c r="DK48" s="47"/>
+      <c r="DL48" s="47"/>
+      <c r="DM48" s="47"/>
+      <c r="DN48" s="47"/>
+      <c r="DO48" s="47"/>
+      <c r="DP48" s="47"/>
+      <c r="DQ48" s="47"/>
+      <c r="DR48" s="47"/>
+      <c r="DS48" s="47"/>
+      <c r="DT48" s="47"/>
+      <c r="DU48" s="47"/>
+      <c r="DV48" s="47"/>
+      <c r="DW48" s="47"/>
+      <c r="DX48" s="47"/>
+      <c r="DY48" s="47"/>
+      <c r="DZ48" s="47"/>
+      <c r="EA48" s="47"/>
+      <c r="EB48" s="47"/>
+      <c r="EC48" s="47"/>
+      <c r="ED48" s="47"/>
+      <c r="EE48" s="47"/>
+      <c r="EF48" s="47"/>
+      <c r="EG48" s="47"/>
+      <c r="EH48" s="47"/>
+      <c r="EI48" s="47"/>
+      <c r="EJ48" s="47"/>
+      <c r="EK48" s="47"/>
+      <c r="EL48" s="47"/>
+      <c r="EM48" s="47"/>
+      <c r="EN48" s="47"/>
+      <c r="EO48" s="47"/>
+      <c r="EP48" s="47"/>
+      <c r="EQ48" s="47"/>
+      <c r="ER48" s="47"/>
+      <c r="ES48" s="47"/>
+      <c r="ET48" s="47"/>
+      <c r="EU48" s="47"/>
+      <c r="EV48" s="47"/>
+      <c r="EW48" s="47"/>
+      <c r="EX48" s="47"/>
+      <c r="EY48" s="47"/>
+      <c r="EZ48" s="47"/>
+      <c r="FA48" s="47"/>
+      <c r="FB48" s="47"/>
+      <c r="FC48" s="47"/>
+      <c r="FD48" s="47"/>
+      <c r="FE48" s="47"/>
+      <c r="FF48" s="47"/>
+      <c r="FG48" s="47"/>
+      <c r="FH48" s="47"/>
+      <c r="FI48" s="47"/>
+      <c r="FJ48" s="47"/>
+      <c r="FK48" s="47"/>
+      <c r="FL48" s="47"/>
+      <c r="FM48" s="47"/>
+      <c r="FN48" s="47"/>
+      <c r="FO48" s="47"/>
+      <c r="FP48" s="47"/>
+      <c r="FQ48" s="47"/>
+      <c r="FR48" s="47"/>
+      <c r="FS48" s="47"/>
+      <c r="FT48" s="47"/>
+      <c r="FU48" s="47"/>
+      <c r="FV48" s="47"/>
+      <c r="FW48" s="47"/>
+      <c r="FX48" s="47"/>
+      <c r="FY48" s="47"/>
+      <c r="FZ48" s="47"/>
+      <c r="GA48" s="47"/>
+      <c r="GB48" s="47"/>
+      <c r="GC48" s="47"/>
+      <c r="GD48" s="47"/>
+      <c r="GE48" s="47"/>
+      <c r="GF48" s="47"/>
+      <c r="GG48" s="47"/>
+      <c r="GH48" s="47"/>
+      <c r="GI48" s="47"/>
+      <c r="GJ48" s="47"/>
+      <c r="GK48" s="47"/>
+      <c r="GL48" s="47"/>
+      <c r="GM48" s="47"/>
+      <c r="GN48" s="47"/>
+      <c r="GO48" s="47"/>
+      <c r="GP48" s="47"/>
+      <c r="GQ48" s="47"/>
+      <c r="GR48" s="47"/>
+      <c r="GS48" s="47"/>
+      <c r="GT48" s="47"/>
+      <c r="GU48" s="47"/>
+      <c r="GV48" s="47"/>
+      <c r="GW48" s="47"/>
+      <c r="GX48" s="47"/>
+      <c r="GY48" s="47"/>
+      <c r="GZ48" s="47"/>
+      <c r="HA48" s="47"/>
+      <c r="HB48" s="47"/>
+      <c r="HC48" s="47"/>
+      <c r="HD48" s="47"/>
+      <c r="HE48" s="47"/>
+      <c r="HF48" s="47"/>
+      <c r="HG48" s="47"/>
+      <c r="HH48" s="47"/>
+      <c r="HI48" s="47"/>
+      <c r="HJ48" s="47"/>
+      <c r="HK48" s="47"/>
+      <c r="HL48" s="47"/>
+      <c r="HM48" s="47"/>
+      <c r="HN48" s="47"/>
+      <c r="HO48" s="47"/>
+      <c r="HP48" s="47"/>
+      <c r="HQ48" s="47"/>
+      <c r="HR48" s="47"/>
+      <c r="HS48" s="47"/>
+      <c r="HT48" s="47"/>
+      <c r="HU48" s="47"/>
+      <c r="HV48" s="47"/>
+      <c r="HW48" s="47"/>
+      <c r="HX48" s="47"/>
+      <c r="HY48" s="47"/>
+      <c r="HZ48" s="47"/>
+      <c r="IA48" s="47"/>
+      <c r="IB48" s="47"/>
+      <c r="IC48" s="47"/>
+      <c r="ID48" s="47"/>
+      <c r="IE48" s="47"/>
+      <c r="IF48" s="47"/>
+      <c r="IG48" s="47"/>
+      <c r="IH48" s="47"/>
+      <c r="II48" s="47"/>
+      <c r="IJ48" s="47"/>
+      <c r="IK48" s="47"/>
+      <c r="IL48" s="47"/>
+      <c r="IM48" s="47"/>
+      <c r="IN48" s="47"/>
+      <c r="IO48" s="47"/>
+      <c r="IP48" s="47"/>
+      <c r="IQ48" s="47"/>
+      <c r="IR48" s="47"/>
+      <c r="IS48" s="47"/>
+      <c r="IT48" s="47"/>
+      <c r="IU48" s="47"/>
+      <c r="IV48" s="47"/>
+      <c r="IW48" s="47"/>
+      <c r="IX48" s="47"/>
     </row>
     <row r="49" spans="1:258" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10"/>
@@ -15265,9 +15233,9 @@
       <c r="N49" s="12"/>
       <c r="O49" s="13"/>
       <c r="P49" s="15"/>
-      <c r="Q49" s="58"/>
-      <c r="R49" s="58" t="s">
-        <v>75</v>
+      <c r="Q49" s="38"/>
+      <c r="R49" s="38" t="s">
+        <v>71</v>
       </c>
       <c r="T49" s="15"/>
       <c r="U49" s="15"/>
@@ -15311,203 +15279,203 @@
       <c r="BG49" s="12"/>
       <c r="BH49" s="12"/>
       <c r="BI49" s="13"/>
-      <c r="BJ49" s="67"/>
-      <c r="BK49" s="67"/>
-      <c r="BL49" s="67"/>
-      <c r="BM49" s="67"/>
-      <c r="BN49" s="67"/>
-      <c r="BO49" s="67"/>
-      <c r="BP49" s="67"/>
-      <c r="BQ49" s="67"/>
-      <c r="BR49" s="67"/>
-      <c r="BS49" s="67"/>
-      <c r="BT49" s="67"/>
-      <c r="BU49" s="67"/>
-      <c r="BV49" s="67"/>
-      <c r="BW49" s="67"/>
-      <c r="BX49" s="67"/>
-      <c r="BY49" s="67"/>
-      <c r="BZ49" s="67"/>
-      <c r="CA49" s="67"/>
-      <c r="CB49" s="67"/>
-      <c r="CC49" s="67"/>
-      <c r="CD49" s="67"/>
-      <c r="CE49" s="67"/>
-      <c r="CF49" s="67"/>
-      <c r="CG49" s="67"/>
-      <c r="CH49" s="67"/>
-      <c r="CI49" s="67"/>
-      <c r="CJ49" s="67"/>
-      <c r="CK49" s="67"/>
-      <c r="CL49" s="67"/>
-      <c r="CM49" s="67"/>
-      <c r="CN49" s="67"/>
-      <c r="CO49" s="67"/>
-      <c r="CP49" s="67"/>
-      <c r="CQ49" s="67"/>
-      <c r="CR49" s="67"/>
-      <c r="CS49" s="67"/>
-      <c r="CT49" s="67"/>
-      <c r="CU49" s="67"/>
-      <c r="CV49" s="67"/>
-      <c r="CW49" s="67"/>
-      <c r="CX49" s="67"/>
-      <c r="CY49" s="67"/>
-      <c r="CZ49" s="67"/>
-      <c r="DA49" s="67"/>
-      <c r="DB49" s="67"/>
-      <c r="DC49" s="67"/>
-      <c r="DD49" s="67"/>
-      <c r="DE49" s="67"/>
-      <c r="DF49" s="67"/>
-      <c r="DG49" s="67"/>
-      <c r="DH49" s="67"/>
-      <c r="DI49" s="67"/>
-      <c r="DJ49" s="67"/>
-      <c r="DK49" s="67"/>
-      <c r="DL49" s="67"/>
-      <c r="DM49" s="67"/>
-      <c r="DN49" s="67"/>
-      <c r="DO49" s="67"/>
-      <c r="DP49" s="67"/>
-      <c r="DQ49" s="67"/>
-      <c r="DR49" s="67"/>
-      <c r="DS49" s="67"/>
-      <c r="DT49" s="67"/>
-      <c r="DU49" s="67"/>
-      <c r="DV49" s="67"/>
-      <c r="DW49" s="67"/>
-      <c r="DX49" s="67"/>
-      <c r="DY49" s="67"/>
-      <c r="DZ49" s="67"/>
-      <c r="EA49" s="67"/>
-      <c r="EB49" s="67"/>
-      <c r="EC49" s="67"/>
-      <c r="ED49" s="67"/>
-      <c r="EE49" s="67"/>
-      <c r="EF49" s="67"/>
-      <c r="EG49" s="67"/>
-      <c r="EH49" s="67"/>
-      <c r="EI49" s="67"/>
-      <c r="EJ49" s="67"/>
-      <c r="EK49" s="67"/>
-      <c r="EL49" s="67"/>
-      <c r="EM49" s="67"/>
-      <c r="EN49" s="67"/>
-      <c r="EO49" s="67"/>
-      <c r="EP49" s="67"/>
-      <c r="EQ49" s="67"/>
-      <c r="ER49" s="67"/>
-      <c r="ES49" s="67"/>
-      <c r="ET49" s="67"/>
-      <c r="EU49" s="67"/>
-      <c r="EV49" s="67"/>
-      <c r="EW49" s="67"/>
-      <c r="EX49" s="67"/>
-      <c r="EY49" s="67"/>
-      <c r="EZ49" s="67"/>
-      <c r="FA49" s="67"/>
-      <c r="FB49" s="67"/>
-      <c r="FC49" s="67"/>
-      <c r="FD49" s="67"/>
-      <c r="FE49" s="67"/>
-      <c r="FF49" s="67"/>
-      <c r="FG49" s="67"/>
-      <c r="FH49" s="67"/>
-      <c r="FI49" s="67"/>
-      <c r="FJ49" s="67"/>
-      <c r="FK49" s="67"/>
-      <c r="FL49" s="67"/>
-      <c r="FM49" s="67"/>
-      <c r="FN49" s="67"/>
-      <c r="FO49" s="67"/>
-      <c r="FP49" s="67"/>
-      <c r="FQ49" s="67"/>
-      <c r="FR49" s="67"/>
-      <c r="FS49" s="67"/>
-      <c r="FT49" s="67"/>
-      <c r="FU49" s="67"/>
-      <c r="FV49" s="67"/>
-      <c r="FW49" s="67"/>
-      <c r="FX49" s="67"/>
-      <c r="FY49" s="67"/>
-      <c r="FZ49" s="67"/>
-      <c r="GA49" s="67"/>
-      <c r="GB49" s="67"/>
-      <c r="GC49" s="67"/>
-      <c r="GD49" s="67"/>
-      <c r="GE49" s="67"/>
-      <c r="GF49" s="67"/>
-      <c r="GG49" s="67"/>
-      <c r="GH49" s="67"/>
-      <c r="GI49" s="67"/>
-      <c r="GJ49" s="67"/>
-      <c r="GK49" s="67"/>
-      <c r="GL49" s="67"/>
-      <c r="GM49" s="67"/>
-      <c r="GN49" s="67"/>
-      <c r="GO49" s="67"/>
-      <c r="GP49" s="67"/>
-      <c r="GQ49" s="67"/>
-      <c r="GR49" s="67"/>
-      <c r="GS49" s="67"/>
-      <c r="GT49" s="67"/>
-      <c r="GU49" s="67"/>
-      <c r="GV49" s="67"/>
-      <c r="GW49" s="67"/>
-      <c r="GX49" s="67"/>
-      <c r="GY49" s="67"/>
-      <c r="GZ49" s="67"/>
-      <c r="HA49" s="67"/>
-      <c r="HB49" s="67"/>
-      <c r="HC49" s="67"/>
-      <c r="HD49" s="67"/>
-      <c r="HE49" s="67"/>
-      <c r="HF49" s="67"/>
-      <c r="HG49" s="67"/>
-      <c r="HH49" s="67"/>
-      <c r="HI49" s="67"/>
-      <c r="HJ49" s="67"/>
-      <c r="HK49" s="67"/>
-      <c r="HL49" s="67"/>
-      <c r="HM49" s="67"/>
-      <c r="HN49" s="67"/>
-      <c r="HO49" s="67"/>
-      <c r="HP49" s="67"/>
-      <c r="HQ49" s="67"/>
-      <c r="HR49" s="67"/>
-      <c r="HS49" s="67"/>
-      <c r="HT49" s="67"/>
-      <c r="HU49" s="67"/>
-      <c r="HV49" s="67"/>
-      <c r="HW49" s="67"/>
-      <c r="HX49" s="67"/>
-      <c r="HY49" s="67"/>
-      <c r="HZ49" s="67"/>
-      <c r="IA49" s="67"/>
-      <c r="IB49" s="67"/>
-      <c r="IC49" s="67"/>
-      <c r="ID49" s="67"/>
-      <c r="IE49" s="67"/>
-      <c r="IF49" s="67"/>
-      <c r="IG49" s="67"/>
-      <c r="IH49" s="67"/>
-      <c r="II49" s="67"/>
-      <c r="IJ49" s="67"/>
-      <c r="IK49" s="67"/>
-      <c r="IL49" s="67"/>
-      <c r="IM49" s="67"/>
-      <c r="IN49" s="67"/>
-      <c r="IO49" s="67"/>
-      <c r="IP49" s="67"/>
-      <c r="IQ49" s="67"/>
-      <c r="IR49" s="67"/>
-      <c r="IS49" s="67"/>
-      <c r="IT49" s="67"/>
-      <c r="IU49" s="67"/>
-      <c r="IV49" s="67"/>
-      <c r="IW49" s="67"/>
-      <c r="IX49" s="67"/>
+      <c r="BJ49" s="47"/>
+      <c r="BK49" s="47"/>
+      <c r="BL49" s="47"/>
+      <c r="BM49" s="47"/>
+      <c r="BN49" s="47"/>
+      <c r="BO49" s="47"/>
+      <c r="BP49" s="47"/>
+      <c r="BQ49" s="47"/>
+      <c r="BR49" s="47"/>
+      <c r="BS49" s="47"/>
+      <c r="BT49" s="47"/>
+      <c r="BU49" s="47"/>
+      <c r="BV49" s="47"/>
+      <c r="BW49" s="47"/>
+      <c r="BX49" s="47"/>
+      <c r="BY49" s="47"/>
+      <c r="BZ49" s="47"/>
+      <c r="CA49" s="47"/>
+      <c r="CB49" s="47"/>
+      <c r="CC49" s="47"/>
+      <c r="CD49" s="47"/>
+      <c r="CE49" s="47"/>
+      <c r="CF49" s="47"/>
+      <c r="CG49" s="47"/>
+      <c r="CH49" s="47"/>
+      <c r="CI49" s="47"/>
+      <c r="CJ49" s="47"/>
+      <c r="CK49" s="47"/>
+      <c r="CL49" s="47"/>
+      <c r="CM49" s="47"/>
+      <c r="CN49" s="47"/>
+      <c r="CO49" s="47"/>
+      <c r="CP49" s="47"/>
+      <c r="CQ49" s="47"/>
+      <c r="CR49" s="47"/>
+      <c r="CS49" s="47"/>
+      <c r="CT49" s="47"/>
+      <c r="CU49" s="47"/>
+      <c r="CV49" s="47"/>
+      <c r="CW49" s="47"/>
+      <c r="CX49" s="47"/>
+      <c r="CY49" s="47"/>
+      <c r="CZ49" s="47"/>
+      <c r="DA49" s="47"/>
+      <c r="DB49" s="47"/>
+      <c r="DC49" s="47"/>
+      <c r="DD49" s="47"/>
+      <c r="DE49" s="47"/>
+      <c r="DF49" s="47"/>
+      <c r="DG49" s="47"/>
+      <c r="DH49" s="47"/>
+      <c r="DI49" s="47"/>
+      <c r="DJ49" s="47"/>
+      <c r="DK49" s="47"/>
+      <c r="DL49" s="47"/>
+      <c r="DM49" s="47"/>
+      <c r="DN49" s="47"/>
+      <c r="DO49" s="47"/>
+      <c r="DP49" s="47"/>
+      <c r="DQ49" s="47"/>
+      <c r="DR49" s="47"/>
+      <c r="DS49" s="47"/>
+      <c r="DT49" s="47"/>
+      <c r="DU49" s="47"/>
+      <c r="DV49" s="47"/>
+      <c r="DW49" s="47"/>
+      <c r="DX49" s="47"/>
+      <c r="DY49" s="47"/>
+      <c r="DZ49" s="47"/>
+      <c r="EA49" s="47"/>
+      <c r="EB49" s="47"/>
+      <c r="EC49" s="47"/>
+      <c r="ED49" s="47"/>
+      <c r="EE49" s="47"/>
+      <c r="EF49" s="47"/>
+      <c r="EG49" s="47"/>
+      <c r="EH49" s="47"/>
+      <c r="EI49" s="47"/>
+      <c r="EJ49" s="47"/>
+      <c r="EK49" s="47"/>
+      <c r="EL49" s="47"/>
+      <c r="EM49" s="47"/>
+      <c r="EN49" s="47"/>
+      <c r="EO49" s="47"/>
+      <c r="EP49" s="47"/>
+      <c r="EQ49" s="47"/>
+      <c r="ER49" s="47"/>
+      <c r="ES49" s="47"/>
+      <c r="ET49" s="47"/>
+      <c r="EU49" s="47"/>
+      <c r="EV49" s="47"/>
+      <c r="EW49" s="47"/>
+      <c r="EX49" s="47"/>
+      <c r="EY49" s="47"/>
+      <c r="EZ49" s="47"/>
+      <c r="FA49" s="47"/>
+      <c r="FB49" s="47"/>
+      <c r="FC49" s="47"/>
+      <c r="FD49" s="47"/>
+      <c r="FE49" s="47"/>
+      <c r="FF49" s="47"/>
+      <c r="FG49" s="47"/>
+      <c r="FH49" s="47"/>
+      <c r="FI49" s="47"/>
+      <c r="FJ49" s="47"/>
+      <c r="FK49" s="47"/>
+      <c r="FL49" s="47"/>
+      <c r="FM49" s="47"/>
+      <c r="FN49" s="47"/>
+      <c r="FO49" s="47"/>
+      <c r="FP49" s="47"/>
+      <c r="FQ49" s="47"/>
+      <c r="FR49" s="47"/>
+      <c r="FS49" s="47"/>
+      <c r="FT49" s="47"/>
+      <c r="FU49" s="47"/>
+      <c r="FV49" s="47"/>
+      <c r="FW49" s="47"/>
+      <c r="FX49" s="47"/>
+      <c r="FY49" s="47"/>
+      <c r="FZ49" s="47"/>
+      <c r="GA49" s="47"/>
+      <c r="GB49" s="47"/>
+      <c r="GC49" s="47"/>
+      <c r="GD49" s="47"/>
+      <c r="GE49" s="47"/>
+      <c r="GF49" s="47"/>
+      <c r="GG49" s="47"/>
+      <c r="GH49" s="47"/>
+      <c r="GI49" s="47"/>
+      <c r="GJ49" s="47"/>
+      <c r="GK49" s="47"/>
+      <c r="GL49" s="47"/>
+      <c r="GM49" s="47"/>
+      <c r="GN49" s="47"/>
+      <c r="GO49" s="47"/>
+      <c r="GP49" s="47"/>
+      <c r="GQ49" s="47"/>
+      <c r="GR49" s="47"/>
+      <c r="GS49" s="47"/>
+      <c r="GT49" s="47"/>
+      <c r="GU49" s="47"/>
+      <c r="GV49" s="47"/>
+      <c r="GW49" s="47"/>
+      <c r="GX49" s="47"/>
+      <c r="GY49" s="47"/>
+      <c r="GZ49" s="47"/>
+      <c r="HA49" s="47"/>
+      <c r="HB49" s="47"/>
+      <c r="HC49" s="47"/>
+      <c r="HD49" s="47"/>
+      <c r="HE49" s="47"/>
+      <c r="HF49" s="47"/>
+      <c r="HG49" s="47"/>
+      <c r="HH49" s="47"/>
+      <c r="HI49" s="47"/>
+      <c r="HJ49" s="47"/>
+      <c r="HK49" s="47"/>
+      <c r="HL49" s="47"/>
+      <c r="HM49" s="47"/>
+      <c r="HN49" s="47"/>
+      <c r="HO49" s="47"/>
+      <c r="HP49" s="47"/>
+      <c r="HQ49" s="47"/>
+      <c r="HR49" s="47"/>
+      <c r="HS49" s="47"/>
+      <c r="HT49" s="47"/>
+      <c r="HU49" s="47"/>
+      <c r="HV49" s="47"/>
+      <c r="HW49" s="47"/>
+      <c r="HX49" s="47"/>
+      <c r="HY49" s="47"/>
+      <c r="HZ49" s="47"/>
+      <c r="IA49" s="47"/>
+      <c r="IB49" s="47"/>
+      <c r="IC49" s="47"/>
+      <c r="ID49" s="47"/>
+      <c r="IE49" s="47"/>
+      <c r="IF49" s="47"/>
+      <c r="IG49" s="47"/>
+      <c r="IH49" s="47"/>
+      <c r="II49" s="47"/>
+      <c r="IJ49" s="47"/>
+      <c r="IK49" s="47"/>
+      <c r="IL49" s="47"/>
+      <c r="IM49" s="47"/>
+      <c r="IN49" s="47"/>
+      <c r="IO49" s="47"/>
+      <c r="IP49" s="47"/>
+      <c r="IQ49" s="47"/>
+      <c r="IR49" s="47"/>
+      <c r="IS49" s="47"/>
+      <c r="IT49" s="47"/>
+      <c r="IU49" s="47"/>
+      <c r="IV49" s="47"/>
+      <c r="IW49" s="47"/>
+      <c r="IX49" s="47"/>
     </row>
     <row r="50" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
@@ -16030,11 +15998,33 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="P14:AS14"/>
+    <mergeCell ref="AT14:BI14"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:O11"/>
+    <mergeCell ref="P11:AD11"/>
+    <mergeCell ref="AE11:BI11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:O12"/>
+    <mergeCell ref="P12:AD12"/>
+    <mergeCell ref="AE12:BI12"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
     <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:BI4"/>
@@ -16051,33 +16041,11 @@
     <mergeCell ref="AT1:AZ1"/>
     <mergeCell ref="BA1:BC1"/>
     <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="P14:AS14"/>
-    <mergeCell ref="AT14:BI14"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:O11"/>
-    <mergeCell ref="P11:AD11"/>
-    <mergeCell ref="AE11:BI11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:O12"/>
-    <mergeCell ref="P12:AD12"/>
-    <mergeCell ref="AE12:BI12"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations disablePrompts="1" count="2">
@@ -16228,18 +16196,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16261,18 +16229,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>